--- a/base_recrutement_luxe_france.xlsx
+++ b/base_recrutement_luxe_france.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Tous les Contacts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Résumé par Groupe" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Résumé par Priorité" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Résumé par Secteur" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tous les Contacts'!$A$1:$K$129</definedName>
@@ -33,7 +30,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="12"/>
     </font>
     <font>
       <color rgb="000563C1"/>
@@ -49,26 +46,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00366092"/>
-        <bgColor rgb="00366092"/>
+        <fgColor rgb="001F4788"/>
+        <bgColor rgb="001F4788"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FF6B6B"/>
+        <bgColor rgb="00FF6B6B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC93C"/>
+        <bgColor rgb="00FFC93C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="0051CF66"/>
+        <bgColor rgb="0051CF66"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -112,24 +109,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -500,16 +479,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1006,7 +985,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Charlotte%20Coupé%20Kenzo</t>
+          <t>https://fr.linkedin.com/in/charlotte-coupé-boudes-4a810023</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1063,7 +1042,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Pascale%20Lepoivre%20Loewe</t>
+          <t>https://fr.linkedin.com/in/pascale-lepoivre-9037331a</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1120,7 +1099,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Emmanuel%20Durand%20Loewe%20HR</t>
+          <t>https://www.linkedin.com/in/emmanuel-durand-87324913/</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1234,7 +1213,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Nicolas%20Wetzel%20Berluti%20HR</t>
+          <t>https://fr.linkedin.com/in/nicolas-wetzel-0b8ab195</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1346,11 +1325,7 @@
           <t>President &amp; CEO Gucci</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Francesca%20Bellettini%20CEO%20Gucci</t>
-        </is>
-      </c>
+      <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Florence/Paris</t>
@@ -1405,7 +1380,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Francesco%20Falai%20Gucci%20CPO</t>
+          <t>https://it.linkedin.com/in/francesco-falai-0815411a</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1462,7 +1437,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Gianfranco%20Gianangeli%20Balenciaga</t>
+          <t>https://it.linkedin.com/in/gianfranco-gianangeli-aa4088138</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1519,7 +1494,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Sophie%20Coustaury%20Balenciaga</t>
+          <t>https://fr.linkedin.com/in/sophie-coustaury-dedeyan-3974226</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2032,7 +2007,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Leena%20Nair%20Chanel%20CEO</t>
+          <t>https://uk.linkedin.com/in/nairleena</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2089,7 +2064,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Larissa%20Zavala%20Chanel</t>
+          <t>https://pa.linkedin.com/in/larissazavala</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2260,7 +2235,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Bartolomeo%20Rongone%20Moncler</t>
+          <t>https://it.linkedin.com/in/bartolomeo-rongone-9a0b873</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -2431,7 +2406,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Bartolomeo%20Rongone</t>
+          <t>https://it.linkedin.com/in/bartolomeo-rongone-9a0b873</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2488,7 +2463,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Gianfranco%20D'Attis%20Alexander%20McQueen</t>
+          <t>https://fr.linkedin.com/in/gianfranco-d'attis/</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2545,7 +2520,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Omer%20Acar%20Raffles</t>
+          <t>https://fr.linkedin.com/in/omer-acar-a9685810</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -3001,7 +2976,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Michael%20Bowes%20Estée%20Lauder</t>
+          <t>https://www.linkedin.com/in/michael-bowes-77164b5/</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
@@ -3229,7 +3204,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Cédric%20Charbit%20Saint%20Laurent</t>
+          <t>https://fr.linkedin.com/in/cedric-charbit-061458b3</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
@@ -5345,7 +5320,11 @@
           <t>Senior VP Human Resources</t>
         </is>
       </c>
-      <c r="H90" s="4" t="inlineStr"/>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/olivier-sastre-a69567112</t>
+        </is>
+      </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -5398,7 +5377,11 @@
           <t>Director of HR International Leather Goods</t>
         </is>
       </c>
-      <c r="H91" s="4" t="inlineStr"/>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cathie-pezard-878aa717/</t>
+        </is>
+      </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
           <t>Île-de-France</t>
@@ -7177,344 +7160,4 @@
   <autoFilter ref="A1:K129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Groupe</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>Nombre de Contacts</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>INDÉPENDANT</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>LVMH</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>KERING</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>RICHEMONT</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>ACCOR</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>LOREAL</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>ESTEE LAUDER</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>ESSILORLUXOTTICA</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Priorité</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>Nombre de Contacts</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="n">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Secteur</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>Nombre de Contacts</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>Mode &amp; Maroquinerie</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>Joaillerie &amp; Montres</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Beauté &amp; Cosmétiques</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Hôtellerie Luxe</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Mode &amp; Accessoires</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Groupe</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Vêtements Premium</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Lunetterie Luxe</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Mode &amp; Parfums</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Mode Luxe</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Parfums &amp; Cosmétiques</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Vins &amp; Spiritueux</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Automobile Luxe</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Distribution</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/base_recrutement_luxe_france.xlsx
+++ b/base_recrutement_luxe_france.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Tous les Contacts" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tous les Contacts'!$A$1:$K$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tous les Contacts'!$A$1:$K$136</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3281,102 +3281,114 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>RICHEMONT</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Van Cleef &amp; Arpels</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr"/>
-      <c r="F50" s="6" t="inlineStr"/>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>HR Team Van Cleef &amp; Arpels</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr"/>
-      <c r="I50" s="6" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Amélie</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Responsable RH Van Cleef &amp; Arpels</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/amelieblanc</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="J50" s="6" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>Joaillerie &amp; Montres</t>
         </is>
       </c>
-      <c r="K50" s="6" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>Important</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>ESSILORLUXOTTICA</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Ray-Ban</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>Francesco</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>Milleri</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>CEO EssilorLuxottica</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Francesco%20Milleri%20EssilorLuxottica</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>Milan/Paris</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>Lunetterie Luxe</t>
-        </is>
-      </c>
-      <c r="K51" s="6" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>RICHEMONT</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Van Cleef &amp; Arpels</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Magali</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Jallot</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director France Van Cleef &amp; Arpels</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/magali-jallot-78939bb</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Joaillerie &amp; Montres</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>Important</t>
         </is>
@@ -3390,52 +3402,52 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>INDÉPENDANT</t>
+          <t>ESSILORLUXOTTICA</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Burberry</t>
+          <t>Ray-Ban</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>HR Director</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Francesco</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Barker</t>
+          <t>Milleri</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Global Talent Director Burberry</t>
+          <t>CEO EssilorLuxottica</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Olivia%20Barker%20Burberry</t>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Francesco%20Milleri%20EssilorLuxottica</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>London/Paris</t>
+          <t>Milan/Paris</t>
         </is>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>Mode &amp; Accessoires</t>
+          <t>Lunetterie Luxe</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>Modéré</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
@@ -3457,32 +3469,32 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>HR Director</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Audra</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Guglielmetti</t>
+          <t>Barker</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>HR Professional Burberry</t>
+          <t>Global Talent Director Burberry</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/audra-guglielmetti/</t>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Olivia%20Barker%20Burberry</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>London/Paris</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
@@ -3509,47 +3521,47 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Ferrari</t>
+          <t>Burberry</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>VP Talent</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Sasa</t>
+          <t>Audra</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Ferrari</t>
+          <t>Guglielmetti</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>VP of Talent Acquisition</t>
+          <t>HR Professional Burberry</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sasa-ferrari-talentacquisition/</t>
+          <t>https://www.linkedin.com/in/audra-guglielmetti/</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>USA/Modena</t>
+          <t>London</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>Automobile Luxe</t>
+          <t>Mode &amp; Accessoires</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>Faible - Niche</t>
+          <t>Modéré</t>
         </is>
       </c>
     </row>
@@ -3571,99 +3583,99 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
+          <t>VP Talent</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Sasa</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Ferrari</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>VP of Talent Acquisition</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sasa-ferrari-talentacquisition/</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>USA/Modena</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>Automobile Luxe</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>Faible - Niche</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Ferrari</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>Glenna</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t>Antczak</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="G56" s="6" t="inlineStr">
         <is>
           <t>HR Professional Ferrari</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/glenna-antczak-27262510/</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t>North America</t>
         </is>
       </c>
-      <c r="J55" s="6" t="inlineStr">
+      <c r="J56" s="6" t="inlineStr">
         <is>
           <t>Automobile Luxe</t>
         </is>
       </c>
-      <c r="K55" s="6" t="inlineStr">
+      <c r="K56" s="6" t="inlineStr">
         <is>
           <t>Faible - Niche</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>LVMH</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Fendi</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Sorenti</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Président Fendi France</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Enrico%20Sorenti%20Fendi</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Mode &amp; Maroquinerie</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Important</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3692,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Céline</t>
+          <t>Fendi</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3688,14 +3700,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Enrico</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Sorenti</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>HR Team Céline</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr"/>
+          <t>Président Fendi France</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Enrico%20Sorenti%20Fendi</t>
+        </is>
+      </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -3725,22 +3749,34 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Givenchy</t>
+          <t>Céline</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Briem</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>HR Team Givenchy</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr"/>
+          <t>Chief HR Officer LVMH Fashion Group</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anna-briem-4a39832/</t>
+        </is>
+      </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -3753,7 +3789,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Modéré</t>
+          <t>TRÈS IMPORTANT</t>
         </is>
       </c>
     </row>
@@ -3770,22 +3806,34 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Bulgari</t>
+          <t>Céline</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="2" t="inlineStr"/>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Michèle</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Amiel</t>
+        </is>
+      </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>HR Team Bulgari</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr"/>
+          <t>DRH LVMH Fashion Activity Group</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/mich%C3%A8le-amiel-a649503b</t>
+        </is>
+      </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -3793,7 +3841,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Joaillerie &amp; Montres</t>
+          <t>Mode &amp; Maroquinerie</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3815,22 +3863,34 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Chaumet</t>
+          <t>Givenchy</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Aymeric</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>HR Team Chaumet</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
+          <t>General Manager Givenchy</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/in/aymeric-martin-88b1466b</t>
+        </is>
+      </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -3838,12 +3898,12 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Joaillerie &amp; Montres</t>
+          <t>Mode &amp; Maroquinerie</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Modéré</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
@@ -3855,47 +3915,47 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>KERING</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Kering HR Team</t>
+          <t>Bulgari</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>HR Director</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Luis Guillermo</t>
+          <t>Isabelle</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Restrepo Angel</t>
+          <t>Castellini</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>HR Professional Kering</t>
+          <t>Human Resources VP Bulgari</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/luisgrestrepo</t>
+          <t>https://www.linkedin.com/in/isabelle-castellini/</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Paris/Rome</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Groupe</t>
+          <t>Joaillerie &amp; Montres</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3912,12 +3972,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>KERING</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Kering HR Team</t>
+          <t>Bulgari</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3927,24 +3987,20 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Jérôme</t>
+          <t>Adélaïde</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Le Brethon</t>
+          <t>de Feuilhade</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>HR Professional Kering</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/jérôme-le-brethon-66752132/</t>
-        </is>
-      </c>
+          <t>Deputy Director HR Bulgari Hotel Paris</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -3952,12 +4008,12 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Groupe</t>
+          <t>Joaillerie &amp; Montres</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Important</t>
+          <t>Modéré</t>
         </is>
       </c>
     </row>
@@ -3969,47 +4025,47 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>KERING</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Saint Laurent</t>
+          <t>Chaumet</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>DRH</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Shelley Xi</t>
+          <t>Caroline</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Yang</t>
+          <t>Clement-Boye</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>HR Professional Saint Laurent</t>
+          <t>HR Director Chaumet Europe</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/shelley-xi-yang/</t>
+          <t>https://www.linkedin.com/in/caroline-clement-boye-a35a121b/</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>China/Paris</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Joaillerie &amp; Montres</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -4026,12 +4082,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>KERING</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Balenciaga</t>
+          <t>Chaumet</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -4039,14 +4095,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Ségolène</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Lorre Denecque</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>HR Team Balenciaga</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr"/>
+          <t>Responsable RH Opérations Chaumet</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/s%C3%A9gol%C3%A8ne-lorre-denecque-106632a6</t>
+        </is>
+      </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -4054,7 +4122,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Joaillerie &amp; Montres</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4071,12 +4139,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>RICHEMONT</t>
+          <t>KERING</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Boucheron</t>
+          <t>Kering HR Team</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4084,14 +4152,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Luis Guillermo</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Restrepo Angel</t>
+        </is>
+      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>HR Team Boucheron</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr"/>
+          <t>HR Professional Kering</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luisgrestrepo</t>
+        </is>
+      </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -4099,7 +4179,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Joaillerie &amp; Montres</t>
+          <t>Groupe</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -4116,12 +4196,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>INDÉPENDANT</t>
+          <t>KERING</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Hermès</t>
+          <t>Kering HR Team</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4131,22 +4211,22 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Jérôme</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Bousselat</t>
+          <t>Le Brethon</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Directrice Ressources Humaines Hermès</t>
+          <t>HR Professional Kering</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/marion-bousselat-185058101</t>
+          <t>https://www.linkedin.com/in/jérôme-le-brethon-66752132/</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -4156,7 +4236,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Groupe</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -4173,12 +4253,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>INDÉPENDANT</t>
+          <t>KERING</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Hermès</t>
+          <t>Saint Laurent</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4188,27 +4268,27 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Shekar</t>
+          <t>Shelley Xi</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Chandra</t>
+          <t>Yang</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Manager HR &amp; Recruitment Hermes Inc</t>
+          <t>HR Professional Saint Laurent</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/shekar-chandra-a76b5862/</t>
+          <t>https://www.linkedin.com/in/shelley-xi-yang/</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>USA/Paris</t>
+          <t>China/Paris</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -4230,42 +4310,42 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>INDÉPENDANT</t>
+          <t>KERING</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Hermès</t>
+          <t>Gucci</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Chief People Officer</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Raffaella</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Ingrao</t>
+          <t>Santoro</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>HR Professional Hermès</t>
+          <t>Chief People Officer EMEA Gucci</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/joanna-ingrao-a2177521/</t>
+          <t>https://www.linkedin.com/in/raffaella-santoro-1812113/</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Paris/Florence</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -4287,730 +4367,790 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
+          <t>KERING</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Gucci</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Lucinda</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Rosso</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>EVP &amp; Chief People Officer Gucci Americas</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lucinda-rosso-97b8225/</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Florence/Paris</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>KERING</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Balenciaga</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Beatrice</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Lazat</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Chief People Officer Kering</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/beatricelazat</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>KERING</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Balenciaga</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>HR Team Balenciaga Extended</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>RICHEMONT</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Boucheron</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Beatrice</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Lazat</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Chief People Officer Kering (covers Boucheron)</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/beatricelazat</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Joaillerie &amp; Montres</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>INDÉPENDANT</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Hermès</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Bousselat</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Directrice Ressources Humaines Hermès</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/marion-bousselat-185058101</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Hermès</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Shekar</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Chandra</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Manager HR &amp; Recruitment Hermes Inc</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shekar-chandra-a76b5862/</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>USA/Paris</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Hermès</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Joanna</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Ingrao</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>HR Professional Hermès</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joanna-ingrao-a2177521/</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Chanel</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>HR Team Chanel Paris</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>Mode &amp; Maroquinerie</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>Important</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>INDÉPENDANT</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>Moncler</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>Lorenzo</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>Cirasaro</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t>Director of Human Resources Europe</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="H77" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=Lorenzo%20Cirasaro%20Moncler</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr">
+      <c r="I77" s="4" t="inlineStr">
         <is>
           <t>Milan/Paris</t>
         </is>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="J77" s="4" t="inlineStr">
         <is>
           <t>Vêtements Premium</t>
         </is>
       </c>
-      <c r="K70" s="4" t="inlineStr">
+      <c r="K77" s="4" t="inlineStr">
         <is>
           <t>Important</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>INDÉPENDANT</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>Moncler</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>Chelsea</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>Gardner</t>
         </is>
       </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="G78" s="4" t="inlineStr">
         <is>
           <t>Human Resources Manager Moncler</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=Chelsea%20Gardner%20Moncler</t>
         </is>
       </c>
-      <c r="I71" s="4" t="inlineStr">
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>Milan</t>
         </is>
       </c>
-      <c r="J71" s="4" t="inlineStr">
+      <c r="J78" s="4" t="inlineStr">
         <is>
           <t>Vêtements Premium</t>
         </is>
       </c>
-      <c r="K71" s="4" t="inlineStr">
+      <c r="K78" s="4" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>INDÉPENDANT</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>Moncler</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>Alexis</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>Velez</t>
         </is>
       </c>
-      <c r="G72" s="4" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t>HR Professional Moncler</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/alexisvelez1/</t>
         </is>
       </c>
-      <c r="I72" s="4" t="inlineStr">
+      <c r="I79" s="4" t="inlineStr">
         <is>
           <t>Milan</t>
         </is>
       </c>
-      <c r="J72" s="4" t="inlineStr">
+      <c r="J79" s="4" t="inlineStr">
         <is>
           <t>Vêtements Premium</t>
         </is>
       </c>
-      <c r="K72" s="4" t="inlineStr">
+      <c r="K79" s="4" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>INDÉPENDANT</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>Prada</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr"/>
-      <c r="F73" s="4" t="inlineStr"/>
-      <c r="G73" s="4" t="inlineStr">
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t>HR Team Prada</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr"/>
-      <c r="I73" s="4" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr">
         <is>
           <t>Milan/Paris</t>
         </is>
       </c>
-      <c r="J73" s="4" t="inlineStr">
+      <c r="J80" s="4" t="inlineStr">
         <is>
           <t>Mode Luxe</t>
         </is>
       </c>
-      <c r="K73" s="4" t="inlineStr">
+      <c r="K80" s="4" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>INDÉPENDANT</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>Brunello Cucinelli</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr"/>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr">
         <is>
           <t>HR Team Brunello Cucinelli</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr"/>
-      <c r="I74" s="4" t="inlineStr">
+      <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" s="4" t="inlineStr">
         <is>
           <t>Pérouse/Paris</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="J81" s="4" t="inlineStr">
         <is>
           <t>Mode Luxe</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr">
+      <c r="K81" s="4" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>ACCOR</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>Sofitel Legend</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>Dalia</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>Kholeef</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr">
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>HR Manager Sofitel Legend</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/people/?keywords=Dalia%20Kholeef%20Sofitel</t>
         </is>
       </c>
-      <c r="I75" s="4" t="inlineStr">
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="J75" s="4" t="inlineStr">
+      <c r="J82" s="4" t="inlineStr">
         <is>
           <t>Hôtellerie Luxe</t>
         </is>
       </c>
-      <c r="K75" s="4" t="inlineStr">
+      <c r="K82" s="4" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>ACCOR</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>Raffles/Fairmont</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr"/>
-      <c r="F76" s="4" t="inlineStr"/>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr">
         <is>
           <t>HR Team Raffles Paris</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr"/>
-      <c r="I76" s="4" t="inlineStr">
+      <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" s="4" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="J76" s="4" t="inlineStr">
+      <c r="J83" s="4" t="inlineStr">
         <is>
           <t>Hôtellerie Luxe</t>
         </is>
       </c>
-      <c r="K76" s="4" t="inlineStr">
+      <c r="K83" s="4" t="inlineStr">
         <is>
           <t>Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>LOREAL</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>L'Oréal Luxe</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>CFO Director</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr"/>
-      <c r="F77" s="6" t="inlineStr"/>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>Finance Team L'Oréal Luxe</t>
-        </is>
-      </c>
-      <c r="H77" s="6" t="inlineStr"/>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="J77" s="6" t="inlineStr">
-        <is>
-          <t>Beauté &amp; Cosmétiques</t>
-        </is>
-      </c>
-      <c r="K77" s="6" t="inlineStr">
-        <is>
-          <t>Modéré</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>LOREAL</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>L'Oréal Luxe</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>Recruitment Coordinator</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr"/>
-      <c r="F78" s="6" t="inlineStr"/>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>Talent Acquisition Coordinator</t>
-        </is>
-      </c>
-      <c r="H78" s="6" t="inlineStr"/>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="J78" s="6" t="inlineStr">
-        <is>
-          <t>Beauté &amp; Cosmétiques</t>
-        </is>
-      </c>
-      <c r="K78" s="6" t="inlineStr">
-        <is>
-          <t>Modéré</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>ESTEE LAUDER</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>Estée Lauder</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>Olivia</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>De Vivo</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>HR Professional Estée Lauder</t>
-        </is>
-      </c>
-      <c r="H79" s="7" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/oliviadevivo/</t>
-        </is>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>New York/Paris</t>
-        </is>
-      </c>
-      <c r="J79" s="6" t="inlineStr">
-        <is>
-          <t>Beauté &amp; Cosmétiques</t>
-        </is>
-      </c>
-      <c r="K79" s="6" t="inlineStr">
-        <is>
-          <t>Modéré</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>RICHEMONT</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>Cartier</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr"/>
-      <c r="F80" s="6" t="inlineStr"/>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>HR Team Cartier Paris</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr"/>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="J80" s="6" t="inlineStr">
-        <is>
-          <t>Joaillerie &amp; Montres</t>
-        </is>
-      </c>
-      <c r="K80" s="6" t="inlineStr">
-        <is>
-          <t>Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>RICHEMONT</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>IWC Schaffhausen</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr"/>
-      <c r="F81" s="6" t="inlineStr"/>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>HR Team IWC</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="inlineStr"/>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>Suisse/Paris</t>
-        </is>
-      </c>
-      <c r="J81" s="6" t="inlineStr">
-        <is>
-          <t>Joaillerie &amp; Montres</t>
-        </is>
-      </c>
-      <c r="K81" s="6" t="inlineStr">
-        <is>
-          <t>Modéré</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>RICHEMONT</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>A. Lange &amp; Söhne</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr"/>
-      <c r="F82" s="6" t="inlineStr"/>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>HR Team A. Lange &amp; Söhne</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr"/>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>Dresde/Paris</t>
-        </is>
-      </c>
-      <c r="J82" s="6" t="inlineStr">
-        <is>
-          <t>Joaillerie &amp; Montres</t>
-        </is>
-      </c>
-      <c r="K82" s="6" t="inlineStr">
-        <is>
-          <t>Modéré</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>RICHEMONT</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>Montblanc</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr"/>
-      <c r="F83" s="6" t="inlineStr"/>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>HR Team Montblanc</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="inlineStr"/>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>Hamburg/Paris</t>
-        </is>
-      </c>
-      <c r="J83" s="6" t="inlineStr">
-        <is>
-          <t>Joaillerie &amp; Montres</t>
-        </is>
-      </c>
-      <c r="K83" s="6" t="inlineStr">
-        <is>
-          <t>Modéré</t>
         </is>
       </c>
     </row>
@@ -5022,35 +5162,35 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>KERING</t>
+          <t>LOREAL</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>Alexander McQueen</t>
+          <t>L'Oréal Luxe</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>CFO Director</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr"/>
       <c r="F84" s="6" t="inlineStr"/>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>HR Team Alexander McQueen</t>
+          <t>Finance Team L'Oréal Luxe</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr"/>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>Paris/Londres</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>Mode &amp; Accessoires</t>
+          <t>Beauté &amp; Cosmétiques</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
@@ -5067,35 +5207,35 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>KERING</t>
+          <t>LOREAL</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Bottega Veneta</t>
+          <t>L'Oréal Luxe</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Recruitment Coordinator</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr"/>
       <c r="F85" s="6" t="inlineStr"/>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>HR Team Bottega Veneta</t>
+          <t>Talent Acquisition Coordinator</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr"/>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>Milan/Paris</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Beauté &amp; Cosmétiques</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
@@ -5112,12 +5252,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>KERING</t>
+          <t>ESTEE LAUDER</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>Brioni</t>
+          <t>Estée Lauder</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -5125,27 +5265,39 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr"/>
-      <c r="F86" s="6" t="inlineStr"/>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>Olivia</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>De Vivo</t>
+        </is>
+      </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>HR Team Brioni</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="inlineStr"/>
+          <t>HR Professional Estée Lauder</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/oliviadevivo/</t>
+        </is>
+      </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>Rome/Paris</t>
+          <t>New York/Paris</t>
         </is>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Beauté &amp; Cosmétiques</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>Faible</t>
+          <t>Modéré</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5309,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>ESSILORLUXOTTICA</t>
+          <t>RICHEMONT</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Persol</t>
+          <t>Cartier</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -5174,18 +5326,18 @@
       <c r="F87" s="6" t="inlineStr"/>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>HR Team Persol</t>
+          <t>HR Team Cartier Paris</t>
         </is>
       </c>
       <c r="H87" s="6" t="inlineStr"/>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>Milan/Paris</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>Lunetterie Luxe</t>
+          <t>Joaillerie &amp; Montres</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
@@ -5202,12 +5354,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>ESSILORLUXOTTICA</t>
+          <t>RICHEMONT</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>Oliver Peoples</t>
+          <t>IWC Schaffhausen</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -5219,23 +5371,23 @@
       <c r="F88" s="6" t="inlineStr"/>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>HR Team Oliver Peoples</t>
+          <t>HR Team IWC</t>
         </is>
       </c>
       <c r="H88" s="6" t="inlineStr"/>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>Milan/Paris</t>
+          <t>Suisse/Paris</t>
         </is>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>Lunetterie Luxe</t>
+          <t>Joaillerie &amp; Montres</t>
         </is>
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>Important</t>
+          <t>Modéré</t>
         </is>
       </c>
     </row>
@@ -5247,12 +5399,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>ESSILORLUXOTTICA</t>
+          <t>RICHEMONT</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Alain Mikli</t>
+          <t>A. Lange &amp; Söhne</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -5264,386 +5416,338 @@
       <c r="F89" s="6" t="inlineStr"/>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>HR Team Alain Mikli</t>
+          <t>HR Team A. Lange &amp; Söhne</t>
         </is>
       </c>
       <c r="H89" s="6" t="inlineStr"/>
       <c r="I89" s="6" t="inlineStr">
         <is>
+          <t>Dresde/Paris</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>Joaillerie &amp; Montres</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>RICHEMONT</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Montblanc</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr"/>
+      <c r="F90" s="6" t="inlineStr"/>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>HR Team Montblanc</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr"/>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>Hamburg/Paris</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>Joaillerie &amp; Montres</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>KERING</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Alexander McQueen</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr"/>
+      <c r="F91" s="6" t="inlineStr"/>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>HR Team Alexander McQueen</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr"/>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>Paris/Londres</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>KERING</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Bottega Veneta</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr"/>
+      <c r="F92" s="6" t="inlineStr"/>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>HR Team Bottega Veneta</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr"/>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>KERING</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Brioni</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr"/>
+      <c r="F93" s="6" t="inlineStr"/>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>HR Team Brioni</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr"/>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>Rome/Paris</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>Faible</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>ESSILORLUXOTTICA</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Persol</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr"/>
+      <c r="F94" s="6" t="inlineStr"/>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>HR Team Persol</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr"/>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>Lunetterie Luxe</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>ESSILORLUXOTTICA</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Oliver Peoples</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr"/>
+      <c r="F95" s="6" t="inlineStr"/>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>HR Team Oliver Peoples</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr"/>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>Lunetterie Luxe</t>
+        </is>
+      </c>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>ESSILORLUXOTTICA</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Alain Mikli</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr"/>
+      <c r="F96" s="6" t="inlineStr"/>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>HR Team Alain Mikli</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr"/>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="J89" s="6" t="inlineStr">
+      <c r="J96" s="6" t="inlineStr">
         <is>
           <t>Lunetterie Luxe</t>
         </is>
       </c>
-      <c r="K89" s="6" t="inlineStr">
+      <c r="K96" s="6" t="inlineStr">
         <is>
           <t>Modéré</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>LVMH</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>Louis Vuitton</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>HR Team Manager</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>Olivier</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>Sastre</t>
-        </is>
-      </c>
-      <c r="G90" s="4" t="inlineStr">
-        <is>
-          <t>Senior VP Human Resources</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>https://fr.linkedin.com/in/olivier-sastre-a69567112</t>
-        </is>
-      </c>
-      <c r="I90" s="4" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>Mode &amp; Maroquinerie</t>
-        </is>
-      </c>
-      <c r="K90" s="4" t="inlineStr">
-        <is>
-          <t>Modéré</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>LVMH</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>Louis Vuitton</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>Cathie</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>Pezard</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>Director of HR International Leather Goods</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/cathie-pezard-878aa717/</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="inlineStr">
-        <is>
-          <t>Île-de-France</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>Mode &amp; Maroquinerie</t>
-        </is>
-      </c>
-      <c r="K91" s="4" t="inlineStr">
-        <is>
-          <t>Modéré</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>LVMH</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>Christian Dior</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>Alexandra</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>De Rancogne</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>HR Professional Christian Dior Couture</t>
-        </is>
-      </c>
-      <c r="H92" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/alexandra-de-rancogne-2347ba7/</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t>Paris/New York</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>Mode &amp; Parfums</t>
-        </is>
-      </c>
-      <c r="K92" s="4" t="inlineStr">
-        <is>
-          <t>Modéré</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>LVMH</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>Christian Dior</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>Nicole</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>Guidry</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t>Director Human Resources Christian Dior</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/nicole-guidry-79458137/</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="inlineStr">
-        <is>
-          <t>USA/Paris</t>
-        </is>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>Mode &amp; Parfums</t>
-        </is>
-      </c>
-      <c r="K93" s="4" t="inlineStr">
-        <is>
-          <t>Modéré</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>LVMH</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>Make Up For Ever</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr"/>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>HR Team Make Up For Ever</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr"/>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>Parfums &amp; Cosmétiques</t>
-        </is>
-      </c>
-      <c r="K94" s="4" t="inlineStr">
-        <is>
-          <t>Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>LVMH</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>Moët &amp; Chandon</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr"/>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>HR Team Moët &amp; Chandon</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr"/>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t>Épernay</t>
-        </is>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>Vins &amp; Spiritueux</t>
-        </is>
-      </c>
-      <c r="K95" s="4" t="inlineStr">
-        <is>
-          <t>Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>LVMH</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>Hennessy</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr"/>
-      <c r="F96" s="4" t="inlineStr"/>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>HR Team Hennessy</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr"/>
-      <c r="I96" s="4" t="inlineStr">
-        <is>
-          <t>Cognac</t>
-        </is>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>Vins &amp; Spiritueux</t>
-        </is>
-      </c>
-      <c r="K96" s="4" t="inlineStr">
-        <is>
-          <t>Important</t>
         </is>
       </c>
     </row>
@@ -5660,22 +5764,34 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Sephora</t>
+          <t>Louis Vuitton</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr"/>
-      <c r="F97" s="4" t="inlineStr"/>
+          <t>HR Team Manager</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Olivier</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>Sastre</t>
+        </is>
+      </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>HR Manager Sephora Paris</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr"/>
+          <t>Senior VP Human Resources</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/olivier-sastre-a69567112</t>
+        </is>
+      </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -5683,12 +5799,12 @@
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Mode &amp; Maroquinerie</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>TRÈS IMPORTANT</t>
+          <t>Modéré</t>
         </is>
       </c>
     </row>
@@ -5700,12 +5816,12 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>KERING</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Gucci</t>
+          <t>Louis Vuitton</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -5713,17 +5829,29 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Cathie</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>Pezard</t>
+        </is>
+      </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>HR Team Gucci Paris</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr"/>
+          <t>Director of HR International Leather Goods</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cathie-pezard-878aa717/</t>
+        </is>
+      </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>Florence/Paris</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
@@ -5733,7 +5861,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Important</t>
+          <t>Modéré</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5873,12 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>KERING</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Saint Laurent</t>
+          <t>Christian Dior</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -5758,27 +5886,39 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr"/>
-      <c r="F99" s="4" t="inlineStr"/>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>De Rancogne</t>
+        </is>
+      </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>HR Team Saint Laurent</t>
-        </is>
-      </c>
-      <c r="H99" s="4" t="inlineStr"/>
+          <t>HR Professional Christian Dior Couture</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alexandra-de-rancogne-2347ba7/</t>
+        </is>
+      </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Paris/New York</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Mode &amp; Parfums</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Important</t>
+          <t>Modéré</t>
         </is>
       </c>
     </row>
@@ -5790,12 +5930,12 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>KERING</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Pomellato</t>
+          <t>Christian Dior</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -5803,22 +5943,34 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr"/>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>Guidry</t>
+        </is>
+      </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>HR Team Pomellato</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr"/>
+          <t>Director Human Resources Christian Dior</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicole-guidry-79458137/</t>
+        </is>
+      </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>Milan/Paris</t>
+          <t>USA/Paris</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>Joaillerie &amp; Montres</t>
+          <t>Mode &amp; Parfums</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
@@ -5828,47 +5980,59 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>KERING</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>Dodo</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr"/>
-      <c r="F101" s="4" t="inlineStr"/>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t>HR Team Dodo</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="inlineStr"/>
-      <c r="I101" s="4" t="inlineStr">
-        <is>
-          <t>Milan/Paris</t>
-        </is>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>Joaillerie &amp; Montres</t>
-        </is>
-      </c>
-      <c r="K101" s="4" t="inlineStr">
-        <is>
-          <t>Faible</t>
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Make Up For Ever</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Meunier</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Global HR Director (now at Guerlain)</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/mathilde-meunier-94828031/</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Parfums &amp; Cosmétiques</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Important</t>
         </is>
       </c>
     </row>
@@ -5880,12 +6044,12 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>RICHEMONT</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Cartier</t>
+          <t>Moët &amp; Chandon</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -5897,18 +6061,18 @@
       <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>Additional HR Team Cartier</t>
+          <t>HR Team Moët &amp; Chandon</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Épernay</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>Joaillerie &amp; Montres</t>
+          <t>Vins &amp; Spiritueux</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
@@ -5925,12 +6089,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>RICHEMONT</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Van Cleef &amp; Arpels</t>
+          <t>Hennessy</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -5942,18 +6106,18 @@
       <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>HR Team Van Cleef &amp; Arpels</t>
+          <t>HR Team Hennessy</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Cognac</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>Joaillerie &amp; Montres</t>
+          <t>Vins &amp; Spiritueux</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
@@ -5970,12 +6134,12 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>RICHEMONT</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Jaeger-LeCoultre</t>
+          <t>Sephora</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -5987,23 +6151,23 @@
       <c r="F104" s="4" t="inlineStr"/>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>HR Team Jaeger-LeCoultre</t>
+          <t>HR Manager Sephora Paris</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>Vallée de Joux</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>Joaillerie &amp; Montres</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>Modéré</t>
+          <t>TRÈS IMPORTANT</t>
         </is>
       </c>
     </row>
@@ -6015,12 +6179,12 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>RICHEMONT</t>
+          <t>KERING</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Vacheron Constantin</t>
+          <t>Gucci</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -6032,23 +6196,23 @@
       <c r="F105" s="4" t="inlineStr"/>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>HR Team Vacheron Constantin</t>
+          <t>HR Team Gucci Paris</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>Genève/Paris</t>
+          <t>Florence/Paris</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>Joaillerie &amp; Montres</t>
+          <t>Mode &amp; Maroquinerie</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>Modéré</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
@@ -6060,12 +6224,12 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>RICHEMONT</t>
+          <t>KERING</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Chloé</t>
+          <t>Saint Laurent</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -6077,7 +6241,7 @@
       <c r="F106" s="4" t="inlineStr"/>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>HR Team Chloé</t>
+          <t>HR Team Saint Laurent</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -6088,7 +6252,7 @@
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>Mode &amp; Accessoires</t>
+          <t>Mode &amp; Maroquinerie</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
@@ -6105,12 +6269,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>RICHEMONT</t>
+          <t>KERING</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Alfred Dunhill</t>
+          <t>Pomellato</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -6122,18 +6286,18 @@
       <c r="F107" s="4" t="inlineStr"/>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>HR Team Alfred Dunhill</t>
+          <t>HR Team Pomellato</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>Londres/Paris</t>
+          <t>Milan/Paris</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>Mode &amp; Accessoires</t>
+          <t>Joaillerie &amp; Montres</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
@@ -6150,12 +6314,12 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>INDÉPENDANT</t>
+          <t>KERING</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Hermès</t>
+          <t>Dodo</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -6163,39 +6327,27 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>Michael</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>Pagan</t>
-        </is>
-      </c>
+      <c r="E108" s="4" t="inlineStr"/>
+      <c r="F108" s="4" t="inlineStr"/>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>Talent Professional Hermès</t>
-        </is>
-      </c>
-      <c r="H108" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/paganmich/</t>
-        </is>
-      </c>
+          <t>HR Team Dodo</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr"/>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>USA/Paris</t>
+          <t>Milan/Paris</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Joaillerie &amp; Montres</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>Modéré</t>
+          <t>Faible</t>
         </is>
       </c>
     </row>
@@ -6207,12 +6359,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>INDÉPENDANT</t>
+          <t>RICHEMONT</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Hermès</t>
+          <t>Cartier</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -6220,39 +6372,27 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>Jim</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>Bures</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>HR Professional Hermès</t>
-        </is>
-      </c>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/jim-bures/</t>
-        </is>
-      </c>
+          <t>Additional HR Team Cartier</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr"/>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>USA/Paris</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Joaillerie &amp; Montres</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>Modéré</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
@@ -6264,24 +6404,24 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>INDÉPENDANT</t>
+          <t>RICHEMONT</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Chanel</t>
+          <t>Van Cleef &amp; Arpels</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Recruiter</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr"/>
       <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Team Chanel</t>
+          <t>HR Team Van Cleef &amp; Arpels</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -6292,7 +6432,7 @@
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Joaillerie &amp; Montres</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
@@ -6309,12 +6449,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>INDÉPENDANT</t>
+          <t>RICHEMONT</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Chanel</t>
+          <t>Jaeger-LeCoultre</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -6326,336 +6466,360 @@
       <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>HR Operations Chanel</t>
+          <t>HR Team Jaeger-LeCoultre</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
       <c r="I111" s="4" t="inlineStr">
         <is>
+          <t>Vallée de Joux</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>Joaillerie &amp; Montres</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>RICHEMONT</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Vacheron Constantin</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>HR Team Vacheron Constantin</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr"/>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>Genève/Paris</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>Joaillerie &amp; Montres</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>RICHEMONT</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Chloé</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>HR Team Chloé</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr"/>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="J111" s="4" t="inlineStr">
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>RICHEMONT</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Alfred Dunhill</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>HR Team Alfred Dunhill</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr"/>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>Londres/Paris</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Hermès</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>Pagan</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>Talent Professional Hermès</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paganmich/</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>USA/Paris</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
         <is>
           <t>Mode &amp; Maroquinerie</t>
         </is>
       </c>
-      <c r="K111" s="4" t="inlineStr">
+      <c r="K115" s="4" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>ACCOR</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>Accor Luxury</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Hermès</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E112" s="6" t="inlineStr"/>
-      <c r="F112" s="6" t="inlineStr"/>
-      <c r="G112" s="6" t="inlineStr">
-        <is>
-          <t>HR Team Accor Luxury</t>
-        </is>
-      </c>
-      <c r="H112" s="6" t="inlineStr"/>
-      <c r="I112" s="6" t="inlineStr">
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>Jim</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>Bures</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>HR Professional Hermès</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jim-bures/</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>USA/Paris</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Chanel</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Recruiter</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Team Chanel</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr"/>
+      <c r="I117" s="4" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="J112" s="6" t="inlineStr">
-        <is>
-          <t>Hôtellerie Luxe</t>
-        </is>
-      </c>
-      <c r="K112" s="6" t="inlineStr">
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K117" s="4" t="inlineStr">
         <is>
           <t>Important</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>ACCOR</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>Fairmont</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Chanel</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E113" s="6" t="inlineStr"/>
-      <c r="F113" s="6" t="inlineStr"/>
-      <c r="G113" s="6" t="inlineStr">
-        <is>
-          <t>HR Team Fairmont Paris</t>
-        </is>
-      </c>
-      <c r="H113" s="6" t="inlineStr"/>
-      <c r="I113" s="6" t="inlineStr">
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>HR Operations Chanel</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr"/>
+      <c r="I118" s="4" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="J113" s="6" t="inlineStr">
-        <is>
-          <t>Hôtellerie Luxe</t>
-        </is>
-      </c>
-      <c r="K113" s="6" t="inlineStr">
-        <is>
-          <t>Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>ACCOR</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>Orient Express</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr"/>
-      <c r="F114" s="6" t="inlineStr"/>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>HR Team Orient Express</t>
-        </is>
-      </c>
-      <c r="H114" s="6" t="inlineStr"/>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="J114" s="6" t="inlineStr">
-        <is>
-          <t>Hôtellerie Luxe</t>
-        </is>
-      </c>
-      <c r="K114" s="6" t="inlineStr">
-        <is>
-          <t>Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>LOREAL</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>L'Oréal Luxe</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>Employer Branding Manager</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr"/>
-      <c r="F115" s="6" t="inlineStr"/>
-      <c r="G115" s="6" t="inlineStr">
-        <is>
-          <t>Employer Branding Team</t>
-        </is>
-      </c>
-      <c r="H115" s="6" t="inlineStr"/>
-      <c r="I115" s="6" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="J115" s="6" t="inlineStr">
-        <is>
-          <t>Beauté &amp; Cosmétiques</t>
-        </is>
-      </c>
-      <c r="K115" s="6" t="inlineStr">
-        <is>
-          <t>Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>ESTEE LAUDER</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>Estée Lauder</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>HR Coordinator</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr"/>
-      <c r="F116" s="6" t="inlineStr"/>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>HR Administrative Team</t>
-        </is>
-      </c>
-      <c r="H116" s="6" t="inlineStr"/>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>New York/Paris</t>
-        </is>
-      </c>
-      <c r="J116" s="6" t="inlineStr">
-        <is>
-          <t>Beauté &amp; Cosmétiques</t>
-        </is>
-      </c>
-      <c r="K116" s="6" t="inlineStr">
-        <is>
-          <t>Modéré</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>LVMH</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>Guerlain</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr"/>
-      <c r="F117" s="6" t="inlineStr"/>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>HR Team Guerlain</t>
-        </is>
-      </c>
-      <c r="H117" s="6" t="inlineStr"/>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>Levallois-Perret</t>
-        </is>
-      </c>
-      <c r="J117" s="6" t="inlineStr">
-        <is>
-          <t>Parfums &amp; Cosmétiques</t>
-        </is>
-      </c>
-      <c r="K117" s="6" t="inlineStr">
-        <is>
-          <t>Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>LVMH</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>Kenzo</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>HR Manager</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr"/>
-      <c r="F118" s="6" t="inlineStr"/>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>HR Team Kenzo</t>
-        </is>
-      </c>
-      <c r="H118" s="6" t="inlineStr"/>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="J118" s="6" t="inlineStr">
+      <c r="J118" s="4" t="inlineStr">
         <is>
           <t>Mode &amp; Maroquinerie</t>
         </is>
       </c>
-      <c r="K118" s="6" t="inlineStr">
+      <c r="K118" s="4" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
@@ -6669,12 +6833,12 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>LVMH</t>
+          <t>ACCOR</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Loewe</t>
+          <t>Accor Luxury</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -6686,7 +6850,7 @@
       <c r="F119" s="6" t="inlineStr"/>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>HR Team Loewe</t>
+          <t>HR Team Accor Luxury</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr"/>
@@ -6697,12 +6861,12 @@
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Hôtellerie Luxe</t>
         </is>
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>Modéré</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
@@ -6714,12 +6878,12 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>LVMH</t>
+          <t>ACCOR</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>Berluti</t>
+          <t>Fairmont</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
@@ -6731,7 +6895,7 @@
       <c r="F120" s="6" t="inlineStr"/>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>HR Team Berluti</t>
+          <t>HR Team Fairmont Paris</t>
         </is>
       </c>
       <c r="H120" s="6" t="inlineStr"/>
@@ -6742,12 +6906,12 @@
       </c>
       <c r="J120" s="6" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Hôtellerie Luxe</t>
         </is>
       </c>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>Modéré</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6923,12 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>KERING</t>
+          <t>ACCOR</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Balenciaga</t>
+          <t>Orient Express</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
@@ -6776,7 +6940,7 @@
       <c r="F121" s="6" t="inlineStr"/>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>HR Team Balenciaga Extended</t>
+          <t>HR Team Orient Express</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr"/>
@@ -6787,12 +6951,12 @@
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Hôtellerie Luxe</t>
         </is>
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>Modéré</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
@@ -6804,24 +6968,24 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>KERING</t>
+          <t>LOREAL</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Gucci</t>
+          <t>L'Oréal Luxe</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>Recruitment Manager</t>
+          <t>Employer Branding Manager</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr"/>
       <c r="F122" s="6" t="inlineStr"/>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>Recruitment Team Gucci</t>
+          <t>Employer Branding Team</t>
         </is>
       </c>
       <c r="H122" s="6" t="inlineStr"/>
@@ -6832,7 +6996,7 @@
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Beauté &amp; Cosmétiques</t>
         </is>
       </c>
       <c r="K122" s="6" t="inlineStr">
@@ -6849,40 +7013,40 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>RICHEMONT</t>
+          <t>ESTEE LAUDER</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Cartier</t>
+          <t>Estée Lauder</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Recruitment Manager</t>
+          <t>HR Coordinator</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr"/>
       <c r="F123" s="6" t="inlineStr"/>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>Recruitment Team Cartier</t>
+          <t>HR Administrative Team</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr"/>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>New York/Paris</t>
         </is>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>Joaillerie &amp; Montres</t>
+          <t>Beauté &amp; Cosmétiques</t>
         </is>
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>Important</t>
+          <t>Modéré</t>
         </is>
       </c>
     </row>
@@ -6894,35 +7058,35 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>INDÉPENDANT</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Hermès</t>
+          <t>Guerlain</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>Recruitment Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr"/>
       <c r="F124" s="6" t="inlineStr"/>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>Recruitment Team Hermès</t>
+          <t>HR Team Guerlain</t>
         </is>
       </c>
       <c r="H124" s="6" t="inlineStr"/>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Levallois-Perret</t>
         </is>
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Parfums &amp; Cosmétiques</t>
         </is>
       </c>
       <c r="K124" s="6" t="inlineStr">
@@ -6939,24 +7103,24 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>INDÉPENDANT</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Chanel</t>
+          <t>Kenzo</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Talent Acquisition Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr"/>
       <c r="F125" s="6" t="inlineStr"/>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>Talent Acquisition Chanel</t>
+          <t>HR Team Kenzo</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr"/>
@@ -6972,7 +7136,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>Important</t>
+          <t>Modéré</t>
         </is>
       </c>
     </row>
@@ -6984,35 +7148,35 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>INDÉPENDANT</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Moncler</t>
+          <t>Loewe</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>Recruitment Coordinator</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr"/>
       <c r="F126" s="6" t="inlineStr"/>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>Recruitment Team Moncler</t>
+          <t>HR Team Loewe</t>
         </is>
       </c>
       <c r="H126" s="6" t="inlineStr"/>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>Paris/Milan</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>Vêtements Premium</t>
+          <t>Mode &amp; Maroquinerie</t>
         </is>
       </c>
       <c r="K126" s="6" t="inlineStr">
@@ -7029,35 +7193,35 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>INDÉPENDANT</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Prada</t>
+          <t>Berluti</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>Recruitment Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr"/>
       <c r="F127" s="6" t="inlineStr"/>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>Recruitment Team Prada</t>
+          <t>HR Team Berluti</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr"/>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>Milan/Paris</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>Mode Luxe</t>
+          <t>Mode &amp; Maroquinerie</t>
         </is>
       </c>
       <c r="K127" s="6" t="inlineStr">
@@ -7074,35 +7238,35 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>INDÉPENDANT</t>
+          <t>KERING</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Burberry</t>
+          <t>Balenciaga</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>Recruitment Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr"/>
       <c r="F128" s="6" t="inlineStr"/>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>Recruitment Team Burberry</t>
+          <t>HR Team Balenciaga Extended</t>
         </is>
       </c>
       <c r="H128" s="6" t="inlineStr"/>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>Londres/Paris</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>Mode &amp; Accessoires</t>
+          <t>Mode &amp; Maroquinerie</t>
         </is>
       </c>
       <c r="K128" s="6" t="inlineStr">
@@ -7119,45 +7283,360 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>ESSILORLUXOTTICA</t>
+          <t>KERING</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Ray-Ban</t>
+          <t>Gucci</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Recruitment Manager</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr"/>
       <c r="F129" s="6" t="inlineStr"/>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>HR Team Ray-Ban</t>
+          <t>Recruitment Team Gucci</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr"/>
       <c r="I129" s="6" t="inlineStr">
         <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K129" s="6" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>RICHEMONT</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>Cartier</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>Recruitment Manager</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr"/>
+      <c r="F130" s="6" t="inlineStr"/>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>Recruitment Team Cartier</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr"/>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="inlineStr">
+        <is>
+          <t>Joaillerie &amp; Montres</t>
+        </is>
+      </c>
+      <c r="K130" s="6" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>Hermès</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>Recruitment Manager</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr"/>
+      <c r="F131" s="6" t="inlineStr"/>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>Recruitment Team Hermès</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr"/>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J131" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K131" s="6" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>Chanel</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr"/>
+      <c r="F132" s="6" t="inlineStr"/>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Chanel</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr"/>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J132" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K132" s="6" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>Moncler</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>Recruitment Coordinator</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr"/>
+      <c r="F133" s="6" t="inlineStr"/>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>Recruitment Team Moncler</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr"/>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
           <t>Paris/Milan</t>
         </is>
       </c>
-      <c r="J129" s="6" t="inlineStr">
+      <c r="J133" s="6" t="inlineStr">
+        <is>
+          <t>Vêtements Premium</t>
+        </is>
+      </c>
+      <c r="K133" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>Prada</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>Recruitment Manager</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr"/>
+      <c r="F134" s="6" t="inlineStr"/>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>Recruitment Team Prada</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr"/>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="inlineStr">
+        <is>
+          <t>Mode Luxe</t>
+        </is>
+      </c>
+      <c r="K134" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>Burberry</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>Recruitment Manager</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr"/>
+      <c r="F135" s="6" t="inlineStr"/>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>Recruitment Team Burberry</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr"/>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>Londres/Paris</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>ESSILORLUXOTTICA</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>Ray-Ban</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr"/>
+      <c r="F136" s="6" t="inlineStr"/>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>HR Team Ray-Ban</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr"/>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>Paris/Milan</t>
+        </is>
+      </c>
+      <c r="J136" s="6" t="inlineStr">
         <is>
           <t>Lunetterie Luxe</t>
         </is>
       </c>
-      <c r="K129" s="6" t="inlineStr">
+      <c r="K136" s="6" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K129"/>
+  <autoFilter ref="A1:K136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/base_recrutement_luxe_france.xlsx
+++ b/base_recrutement_luxe_france.xlsx
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Anne%20Journu%20Berluti</t>
+          <t>https://fr.linkedin.com/in/anne-sophie-journu-84721829</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Francesco%20Milleri%20EssilorLuxottica</t>
+          <t>https://it.linkedin.com/in/francesco-milleri</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Olivia%20Barker%20Burberry</t>
+          <t>https://uk.linkedin.com/in/olivia-barker-a3bb22128</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Enrico%20Sorenti%20Fendi</t>
+          <t>https://www.linkedin.com/in/enrico-sorenti-0976a115/</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Lorenzo%20Cirasaro%20Moncler</t>
+          <t>https://fr.linkedin.com/in/lorenzo-cirasaro-3116b213</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">

--- a/base_recrutement_luxe_france.xlsx
+++ b/base_recrutement_luxe_france.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Tous les Contacts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Résumé par Groupe" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Résumé par Priorité" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Résumé par Secteur" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tous les Contacts'!$A$1:$K$136</definedName>
@@ -30,7 +33,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
     </font>
     <font>
       <color rgb="000563C1"/>
@@ -46,8 +48,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4788"/>
-        <bgColor rgb="001F4788"/>
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
@@ -87,9 +89,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -110,6 +112,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -478,17 +483,17 @@
   <dimension ref="A1:K136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1325,7 +1330,11 @@
           <t>President &amp; CEO Gucci</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/francesca-bellettini-45729a114/</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Florence/Paris</t>
@@ -4000,7 +4009,11 @@
           <t>Deputy Director HR Bulgari Hotel Paris</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adélaïde-de-feuilhade/</t>
+        </is>
+      </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -4501,7 +4514,11 @@
           <t>HR Team Balenciaga Extended</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/sophie-coustaury-dedeyan-3974226</t>
+        </is>
+      </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -4774,7 +4791,11 @@
           <t>HR Team Chanel Paris</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/larissazavala/</t>
+        </is>
+      </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -4990,7 +5011,11 @@
           <t>HR Team Prada</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>https://theorg.com/org/prada-spa/org-chart/rosa-santamaria</t>
+        </is>
+      </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
           <t>Milan/Paris</t>
@@ -5035,7 +5060,11 @@
           <t>HR Team Brunello Cucinelli</t>
         </is>
       </c>
-      <c r="H81" s="4" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fashionhr/</t>
+        </is>
+      </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
           <t>Pérouse/Paris</t>
@@ -5137,7 +5166,11 @@
           <t>HR Team Raffles Paris</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr"/>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/srevillion</t>
+        </is>
+      </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -5329,7 +5362,11 @@
           <t>HR Team Cartier Paris</t>
         </is>
       </c>
-      <c r="H87" s="6" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/zyla-akiti-790943aa/</t>
+        </is>
+      </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -5374,7 +5411,11 @@
           <t>HR Team IWC</t>
         </is>
       </c>
-      <c r="H88" s="6" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/nikki-cartwright-b5a30127</t>
+        </is>
+      </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
           <t>Suisse/Paris</t>
@@ -5464,7 +5505,11 @@
           <t>HR Team Montblanc</t>
         </is>
       </c>
-      <c r="H90" s="6" t="inlineStr"/>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/emanuela-bontempelli-1261a8b</t>
+        </is>
+      </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
           <t>Hamburg/Paris</t>
@@ -5509,7 +5554,11 @@
           <t>HR Team Alexander McQueen</t>
         </is>
       </c>
-      <c r="H91" s="6" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/ella-morgan-crosby-308a093b</t>
+        </is>
+      </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
           <t>Paris/Londres</t>
@@ -5554,7 +5603,11 @@
           <t>HR Team Bottega Veneta</t>
         </is>
       </c>
-      <c r="H92" s="6" t="inlineStr"/>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ioanaandreeazeres/?_l=en</t>
+        </is>
+      </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
           <t>Milan/Paris</t>
@@ -5644,7 +5697,11 @@
           <t>HR Team Persol</t>
         </is>
       </c>
-      <c r="H94" s="6" t="inlineStr"/>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emilene-rocha-shrm-scp/</t>
+        </is>
+      </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
           <t>Milan/Paris</t>
@@ -6064,7 +6121,11 @@
           <t>HR Team Moët &amp; Chandon</t>
         </is>
       </c>
-      <c r="H102" s="4" t="inlineStr"/>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/claire-de-coincy-b30a5740</t>
+        </is>
+      </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
           <t>Épernay</t>
@@ -6154,7 +6215,11 @@
           <t>HR Manager Sephora Paris</t>
         </is>
       </c>
-      <c r="H104" s="4" t="inlineStr"/>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/linda-skinner-4a7b6615/</t>
+        </is>
+      </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -6808,7 +6873,11 @@
           <t>HR Operations Chanel</t>
         </is>
       </c>
-      <c r="H118" s="4" t="inlineStr"/>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maxine-malikin-b255b250/</t>
+        </is>
+      </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -7258,7 +7327,11 @@
           <t>HR Team Balenciaga Extended</t>
         </is>
       </c>
-      <c r="H128" s="6" t="inlineStr"/>
+      <c r="H128" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elena-mccoy-47180629a/</t>
+        </is>
+      </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -7637,6 +7710,436 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K136"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId100"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Groupe</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Nombre de Contacts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ACCOR</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ESSILORLUXOTTICA</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KERING</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LOREAL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RICHEMONT</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Priorité</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Nombre de Contacts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Secteur</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Nombre de Contacts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Automobile Luxe</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Beauté &amp; Cosmétiques</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Groupe</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Hôtellerie Luxe</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Joaillerie &amp; Montres</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lunetterie Luxe</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mode &amp; Parfums</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mode Luxe</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Parfums &amp; Cosmétiques</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Vins &amp; Spiritueux</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Vêtements Premium</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/base_recrutement_luxe_france.xlsx
+++ b/base_recrutement_luxe_france.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Tous les Contacts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Résumé par Groupe" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Résumé par Priorité" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Résumé par Secteur" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tous les Contacts'!$A$1:$K$136</definedName>
@@ -89,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -112,9 +109,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4507,8 +4501,16 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Coustaury</t>
+        </is>
+      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>HR Team Balenciaga Extended</t>
@@ -4784,8 +4786,16 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Zavala</t>
+        </is>
+      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
           <t>HR Team Chanel Paris</t>
@@ -5004,8 +5014,16 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Santamaria Maurizio</t>
+        </is>
+      </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
           <t>HR Team Prada</t>
@@ -5053,8 +5071,16 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr"/>
-      <c r="F81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Aisha</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Rosenfeld</t>
+        </is>
+      </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
           <t>HR Team Brunello Cucinelli</t>
@@ -5159,8 +5185,16 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr"/>
-      <c r="F83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Salomé</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Révillion</t>
+        </is>
+      </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
           <t>HR Team Raffles Paris</t>
@@ -5208,14 +5242,26 @@
           <t>CFO Director</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr"/>
-      <c r="F84" s="6" t="inlineStr"/>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>Lilian</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>Tran</t>
+        </is>
+      </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
           <t>Finance Team L'Oréal Luxe</t>
         </is>
       </c>
-      <c r="H84" s="6" t="inlineStr"/>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/liliantranhrprofessional</t>
+        </is>
+      </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -5253,14 +5299,26 @@
           <t>Recruitment Coordinator</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr"/>
-      <c r="F85" s="6" t="inlineStr"/>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>Silva</t>
+        </is>
+      </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
           <t>Talent Acquisition Coordinator</t>
         </is>
       </c>
-      <c r="H85" s="6" t="inlineStr"/>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/patricia-silva-76b9bb80</t>
+        </is>
+      </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -5355,8 +5413,16 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr"/>
-      <c r="F87" s="6" t="inlineStr"/>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>Zyla</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>Akiti</t>
+        </is>
+      </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
           <t>HR Team Cartier Paris</t>
@@ -5404,8 +5470,16 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr"/>
-      <c r="F88" s="6" t="inlineStr"/>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Nikki</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>Cartwright</t>
+        </is>
+      </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
           <t>HR Team IWC</t>
@@ -5453,14 +5527,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr"/>
-      <c r="F89" s="6" t="inlineStr"/>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>Susan</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>Richter</t>
+        </is>
+      </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
           <t>HR Team A. Lange &amp; Söhne</t>
         </is>
       </c>
-      <c r="H89" s="6" t="inlineStr"/>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/susan-richter-901a2a89/</t>
+        </is>
+      </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
           <t>Dresde/Paris</t>
@@ -5498,8 +5584,16 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr"/>
-      <c r="F90" s="6" t="inlineStr"/>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Emanuela</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>Bontempelli</t>
+        </is>
+      </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
           <t>HR Team Montblanc</t>
@@ -5547,8 +5641,16 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr"/>
-      <c r="F91" s="6" t="inlineStr"/>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Morgan-Crosby</t>
+        </is>
+      </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
           <t>HR Team Alexander McQueen</t>
@@ -5596,8 +5698,16 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr"/>
-      <c r="F92" s="6" t="inlineStr"/>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>Ioana</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>Zeres</t>
+        </is>
+      </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
           <t>HR Team Bottega Veneta</t>
@@ -5645,14 +5755,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr"/>
-      <c r="F93" s="6" t="inlineStr"/>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Alessandro</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>Paparelli</t>
+        </is>
+      </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
           <t>HR Team Brioni</t>
         </is>
       </c>
-      <c r="H93" s="6" t="inlineStr"/>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/alessandropaparelli</t>
+        </is>
+      </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
           <t>Rome/Paris</t>
@@ -5690,8 +5812,16 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr"/>
-      <c r="F94" s="6" t="inlineStr"/>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Emilene</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>Rocha</t>
+        </is>
+      </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
           <t>HR Team Persol</t>
@@ -5739,14 +5869,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr"/>
-      <c r="F95" s="6" t="inlineStr"/>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Rocco</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>Basilico</t>
+        </is>
+      </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
           <t>HR Team Oliver Peoples</t>
         </is>
       </c>
-      <c r="H95" s="6" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rocco-basilico-62055016a/</t>
+        </is>
+      </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
           <t>Milan/Paris</t>
@@ -6114,8 +6256,16 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr"/>
-      <c r="F102" s="4" t="inlineStr"/>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>Claire</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>de Coincy</t>
+        </is>
+      </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
           <t>HR Team Moët &amp; Chandon</t>
@@ -6163,14 +6313,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr"/>
-      <c r="F103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Fanny</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>Peraldi</t>
+        </is>
+      </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
           <t>HR Team Hennessy</t>
         </is>
       </c>
-      <c r="H103" s="4" t="inlineStr"/>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/fanny-peraldi-67a5b71</t>
+        </is>
+      </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
           <t>Cognac</t>
@@ -6208,8 +6370,16 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr"/>
-      <c r="F104" s="4" t="inlineStr"/>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>Skinner</t>
+        </is>
+      </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
           <t>HR Manager Sephora Paris</t>
@@ -6257,14 +6427,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E105" s="4" t="inlineStr"/>
-      <c r="F105" s="4" t="inlineStr"/>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Joane</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>Daoud</t>
+        </is>
+      </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
           <t>HR Team Gucci Paris</t>
         </is>
       </c>
-      <c r="H105" s="4" t="inlineStr"/>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joane-daoud-611631208/</t>
+        </is>
+      </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
           <t>Florence/Paris</t>
@@ -6302,14 +6484,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr"/>
-      <c r="F106" s="4" t="inlineStr"/>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
           <t>HR Team Saint Laurent</t>
         </is>
       </c>
-      <c r="H106" s="4" t="inlineStr"/>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/laura-green-7b153b197/</t>
+        </is>
+      </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -6347,14 +6541,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr"/>
-      <c r="F107" s="4" t="inlineStr"/>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Prisca</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>Centaure</t>
+        </is>
+      </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
           <t>HR Team Pomellato</t>
         </is>
       </c>
-      <c r="H107" s="4" t="inlineStr"/>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/priscacentaure/</t>
+        </is>
+      </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
           <t>Milan/Paris</t>
@@ -6437,14 +6643,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr"/>
-      <c r="F109" s="4" t="inlineStr"/>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Claire-Lise</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>Pelé Hemeryck</t>
+        </is>
+      </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
           <t>Additional HR Team Cartier</t>
         </is>
       </c>
-      <c r="H109" s="4" t="inlineStr"/>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/claire-lise-pel%C3%A9-hemeryck-aa97a043/</t>
+        </is>
+      </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -6482,14 +6700,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr"/>
-      <c r="F110" s="4" t="inlineStr"/>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Aurélie</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>Benard</t>
+        </is>
+      </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
           <t>HR Team Van Cleef &amp; Arpels</t>
         </is>
       </c>
-      <c r="H110" s="4" t="inlineStr"/>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/in/aur%C3%A9lie-benard-a780832a</t>
+        </is>
+      </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -6527,14 +6757,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr"/>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Céline</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>J.</t>
+        </is>
+      </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
           <t>HR Team Jaeger-LeCoultre</t>
         </is>
       </c>
-      <c r="H111" s="4" t="inlineStr"/>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>https://ch.linkedin.com/in/cjeffredo/en</t>
+        </is>
+      </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
           <t>Vallée de Joux</t>
@@ -6572,14 +6814,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr"/>
-      <c r="F112" s="4" t="inlineStr"/>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>Travis</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>Bassett</t>
+        </is>
+      </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
           <t>HR Team Vacheron Constantin</t>
         </is>
       </c>
-      <c r="H112" s="4" t="inlineStr"/>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/travis-bassett032886/</t>
+        </is>
+      </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
           <t>Genève/Paris</t>
@@ -6617,14 +6871,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr"/>
-      <c r="F113" s="4" t="inlineStr"/>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>Chloé</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>Athlan</t>
+        </is>
+      </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
           <t>HR Team Chloé</t>
         </is>
       </c>
-      <c r="H113" s="4" t="inlineStr"/>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/chlo%C3%A9-athlan-a3138964</t>
+        </is>
+      </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -6662,14 +6928,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr"/>
-      <c r="F114" s="4" t="inlineStr"/>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Leah</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>Jones</t>
+        </is>
+      </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
           <t>HR Team Alfred Dunhill</t>
         </is>
       </c>
-      <c r="H114" s="4" t="inlineStr"/>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/leah-jones-a738a54</t>
+        </is>
+      </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
           <t>Londres/Paris</t>
@@ -6821,14 +7099,26 @@
           <t>Recruiter</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr"/>
-      <c r="F117" s="4" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Shari</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>Katz</t>
+        </is>
+      </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
           <t>Talent Acquisition Team Chanel</t>
         </is>
       </c>
-      <c r="H117" s="4" t="inlineStr"/>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shari-katz-recruiter/</t>
+        </is>
+      </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -6866,8 +7156,16 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr"/>
-      <c r="F118" s="4" t="inlineStr"/>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Maxine</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>Malikin</t>
+        </is>
+      </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
           <t>HR Operations Chanel</t>
@@ -6915,14 +7213,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr"/>
-      <c r="F119" s="6" t="inlineStr"/>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>Sucheta</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>Banik</t>
+        </is>
+      </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
           <t>HR Team Accor Luxury</t>
         </is>
       </c>
-      <c r="H119" s="6" t="inlineStr"/>
+      <c r="H119" s="7" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/in/sucheta-banik-299924174</t>
+        </is>
+      </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -7005,14 +7315,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E121" s="6" t="inlineStr"/>
-      <c r="F121" s="6" t="inlineStr"/>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>Insam</t>
+        </is>
+      </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
           <t>HR Team Orient Express</t>
         </is>
       </c>
-      <c r="H121" s="6" t="inlineStr"/>
+      <c r="H121" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrea-insam/</t>
+        </is>
+      </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -7050,14 +7372,26 @@
           <t>Employer Branding Manager</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr"/>
-      <c r="F122" s="6" t="inlineStr"/>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>F.</t>
+        </is>
+      </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
           <t>Employer Branding Team</t>
         </is>
       </c>
-      <c r="H122" s="6" t="inlineStr"/>
+      <c r="H122" s="7" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/sarah-f-98704b87</t>
+        </is>
+      </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -7095,14 +7429,26 @@
           <t>HR Coordinator</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr"/>
-      <c r="F123" s="6" t="inlineStr"/>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>Curran</t>
+        </is>
+      </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
           <t>HR Administrative Team</t>
         </is>
       </c>
-      <c r="H123" s="6" t="inlineStr"/>
+      <c r="H123" s="7" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/sarah-curran-aa341228</t>
+        </is>
+      </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
           <t>New York/Paris</t>
@@ -7320,8 +7666,16 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E128" s="6" t="inlineStr"/>
-      <c r="F128" s="6" t="inlineStr"/>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>McCoy</t>
+        </is>
+      </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
           <t>HR Team Balenciaga Extended</t>
@@ -7369,14 +7723,26 @@
           <t>Recruitment Manager</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr"/>
-      <c r="F129" s="6" t="inlineStr"/>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>Sébastien</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>Hueber</t>
+        </is>
+      </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
           <t>Recruitment Team Gucci</t>
         </is>
       </c>
-      <c r="H129" s="6" t="inlineStr"/>
+      <c r="H129" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/s%C3%A9bastien-hueber-24491011a/</t>
+        </is>
+      </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -7414,14 +7780,26 @@
           <t>Recruitment Manager</t>
         </is>
       </c>
-      <c r="E130" s="6" t="inlineStr"/>
-      <c r="F130" s="6" t="inlineStr"/>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>Linley</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>Howley</t>
+        </is>
+      </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
           <t>Recruitment Team Cartier</t>
         </is>
       </c>
-      <c r="H130" s="6" t="inlineStr"/>
+      <c r="H130" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/linley-howley-22249a228/</t>
+        </is>
+      </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -7459,14 +7837,26 @@
           <t>Recruitment Manager</t>
         </is>
       </c>
-      <c r="E131" s="6" t="inlineStr"/>
-      <c r="F131" s="6" t="inlineStr"/>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>Clarisse</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>Gourier</t>
+        </is>
+      </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
           <t>Recruitment Team Hermès</t>
         </is>
       </c>
-      <c r="H131" s="6" t="inlineStr"/>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/clarisse-gourier-5aba97ba/en</t>
+        </is>
+      </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -7504,14 +7894,26 @@
           <t>Talent Acquisition Manager</t>
         </is>
       </c>
-      <c r="E132" s="6" t="inlineStr"/>
-      <c r="F132" s="6" t="inlineStr"/>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>Levine</t>
+        </is>
+      </c>
       <c r="G132" s="6" t="inlineStr">
         <is>
           <t>Talent Acquisition Chanel</t>
         </is>
       </c>
-      <c r="H132" s="6" t="inlineStr"/>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lorilevine1001/</t>
+        </is>
+      </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -7639,14 +8041,26 @@
           <t>Recruitment Manager</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr"/>
-      <c r="F135" s="6" t="inlineStr"/>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>Melody</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
           <t>Recruitment Team Burberry</t>
         </is>
       </c>
-      <c r="H135" s="6" t="inlineStr"/>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/melody-small-683a6a27b/</t>
+        </is>
+      </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
           <t>Londres/Paris</t>
@@ -7684,14 +8098,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr"/>
-      <c r="F136" s="6" t="inlineStr"/>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>Madan</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>Kapoor</t>
+        </is>
+      </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
           <t>HR Team Ray-Ban</t>
         </is>
       </c>
-      <c r="H136" s="6" t="inlineStr"/>
+      <c r="H136" s="7" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/in/madan-kapoor-72a038297</t>
+        </is>
+      </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
           <t>Paris/Milan</t>
@@ -7793,353 +8219,51 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId126"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Groupe</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nombre de Contacts</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACCOR</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ESSILORLUXOTTICA</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ESTEE LAUDER</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>INDÉPENDANT</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>KERING</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LOREAL</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LVMH</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RICHEMONT</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>18</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Priorité</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nombre de Contacts</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>42</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Secteur</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nombre de Contacts</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Automobile Luxe</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Beauté &amp; Cosmétiques</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Distribution</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Groupe</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Hôtellerie Luxe</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Joaillerie &amp; Montres</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Lunetterie Luxe</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Mode &amp; Accessoires</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Mode &amp; Maroquinerie</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Mode &amp; Parfums</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Mode Luxe</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Parfums &amp; Cosmétiques</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Vins &amp; Spiritueux</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Vêtements Premium</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/base_recrutement_luxe_france.xlsx
+++ b/base_recrutement_luxe_france.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Tous les Contacts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Résumé par Groupe" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Résumé par Priorité" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Résumé par Secteur" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tous les Contacts'!$A$1:$K$136</definedName>
@@ -5926,14 +5929,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr"/>
-      <c r="F96" s="6" t="inlineStr"/>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>Maxime</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>Maigne</t>
+        </is>
+      </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
           <t>HR Team Alain Mikli</t>
         </is>
       </c>
-      <c r="H96" s="6" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maxime-maigne/</t>
+        </is>
+      </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -6598,14 +6613,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr"/>
-      <c r="F108" s="4" t="inlineStr"/>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>de Dominicis</t>
+        </is>
+      </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
           <t>HR Team Dodo</t>
         </is>
       </c>
-      <c r="H108" s="4" t="inlineStr"/>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/camille-de-dominicis-4893aa13</t>
+        </is>
+      </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
           <t>Milan/Paris</t>
@@ -7270,14 +7297,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr"/>
-      <c r="F120" s="6" t="inlineStr"/>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>Liz</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>George</t>
+        </is>
+      </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
           <t>HR Team Fairmont Paris</t>
         </is>
       </c>
-      <c r="H120" s="6" t="inlineStr"/>
+      <c r="H120" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/liz-george-1756ab30/</t>
+        </is>
+      </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -7486,14 +7525,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr"/>
-      <c r="F124" s="6" t="inlineStr"/>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>Saint-Genis</t>
+        </is>
+      </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
           <t>HR Team Guerlain</t>
         </is>
       </c>
-      <c r="H124" s="6" t="inlineStr"/>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/gabrielle-saint-genis-67148415</t>
+        </is>
+      </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
           <t>Levallois-Perret</t>
@@ -7531,14 +7582,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E125" s="6" t="inlineStr"/>
-      <c r="F125" s="6" t="inlineStr"/>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>Gaël</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>Laudet</t>
+        </is>
+      </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
           <t>HR Team Kenzo</t>
         </is>
       </c>
-      <c r="H125" s="6" t="inlineStr"/>
+      <c r="H125" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ga%C3%ABl-laudet-85616b150/</t>
+        </is>
+      </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -7576,14 +7639,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr"/>
-      <c r="F126" s="6" t="inlineStr"/>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>Lluís</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>Colom</t>
+        </is>
+      </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
           <t>HR Team Loewe</t>
         </is>
       </c>
-      <c r="H126" s="6" t="inlineStr"/>
+      <c r="H126" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/llu%C3%ADscolom/</t>
+        </is>
+      </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -7621,14 +7696,26 @@
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr"/>
-      <c r="F127" s="6" t="inlineStr"/>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>Atsushi</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>Yatera</t>
+        </is>
+      </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
           <t>HR Team Berluti</t>
         </is>
       </c>
-      <c r="H127" s="6" t="inlineStr"/>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/atsushi-yatera-6975b94b/</t>
+        </is>
+      </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -7951,14 +8038,26 @@
           <t>Recruitment Coordinator</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr"/>
-      <c r="F133" s="6" t="inlineStr"/>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>Carine</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>Le Ny</t>
+        </is>
+      </c>
       <c r="G133" s="6" t="inlineStr">
         <is>
           <t>Recruitment Team Moncler</t>
         </is>
       </c>
-      <c r="H133" s="6" t="inlineStr"/>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carine-le-ny-b27b64b/</t>
+        </is>
+      </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
           <t>Paris/Milan</t>
@@ -7996,14 +8095,26 @@
           <t>Recruitment Manager</t>
         </is>
       </c>
-      <c r="E134" s="6" t="inlineStr"/>
-      <c r="F134" s="6" t="inlineStr"/>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>Martina</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>Righeschi</t>
+        </is>
+      </c>
       <c r="G134" s="6" t="inlineStr">
         <is>
           <t>Recruitment Team Prada</t>
         </is>
       </c>
-      <c r="H134" s="6" t="inlineStr"/>
+      <c r="H134" s="7" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/martina-righeschi-4a07a4b</t>
+        </is>
+      </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
           <t>Milan/Paris</t>
@@ -8231,39 +8342,376 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId135"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Groupe</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Contacts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ACCOR</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ESSILORLUXOTTICA</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KERING</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LOREAL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RICHEMONT</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Priorité</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Contacts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Secteur</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Contacts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Automobile Luxe</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Beauté &amp; Cosmétiques</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Groupe</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Hôtellerie Luxe</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Joaillerie &amp; Montres</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lunetterie Luxe</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mode &amp; Parfums</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mode Luxe</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Parfums &amp; Cosmétiques</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Vins &amp; Spiritueux</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Vêtements Premium</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/base_recrutement_luxe_france.xlsx
+++ b/base_recrutement_luxe_france.xlsx
@@ -12,9 +12,7 @@
     <sheet name="Résumé par Priorité" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Résumé par Secteur" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tous les Contacts'!$A$1:$K$136</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -48,8 +46,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="00366092"/>
+        <bgColor rgb="00366092"/>
       </patternFill>
     </fill>
     <fill>
@@ -71,19 +69,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -92,26 +84,14 @@
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -477,20 +457,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K136"/>
+  <dimension ref="A1:K148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8245,8 +8225,691 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>KERING</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>Balenciaga</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>Mary</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>HR Director Balenciaga</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mary-miller-051051282/</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>KERING</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>Balenciaga</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>HR Business Partner</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>Hannah</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>Lord</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>HR Business Partner Balenciaga</t>
+        </is>
+      </c>
+      <c r="H138" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hannahmartinlord/</t>
+        </is>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K138" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>Chanel</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>HR Systems Manager</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>Rebecca</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>Bragg</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>HR Systems Manager Chanel</t>
+        </is>
+      </c>
+      <c r="H139" s="7" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/rebecca-bragg-562398a3</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J139" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K139" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Prada</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>Valentina</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>Verchiani</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>HR Director Prada</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/valentina-verchiani/</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>Mode Luxe</t>
+        </is>
+      </c>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>LOREAL</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Sephora</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>EVP Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>Corey</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>Yribarren</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>EVP Chief People Officer Sephora</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/corey-yribarren-07078a3</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>Beauté &amp; Cosmétiques</t>
+        </is>
+      </c>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>TRÈS IMPORTANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>LOREAL</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>Sephora</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>HR Professional</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>Kelly</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>Petersen Davis</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>HR Professional Sephora</t>
+        </is>
+      </c>
+      <c r="H142" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kelly-petersen-davis-aa37a91a/</t>
+        </is>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J142" s="6" t="inlineStr">
+        <is>
+          <t>Beauté &amp; Cosmétiques</t>
+        </is>
+      </c>
+      <c r="K142" s="6" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>LOREAL</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>L'Oréal Luxe</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>HR Learning Coordinator</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>Guéniot</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>HR Learning Coordinator L'Oréal Luxe</t>
+        </is>
+      </c>
+      <c r="H143" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/audrey-guéniot-69a9a35a/</t>
+        </is>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="inlineStr">
+        <is>
+          <t>Beauté &amp; Cosmétiques</t>
+        </is>
+      </c>
+      <c r="K143" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>LOREAL</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>L'Oréal Luxe</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>Head of HR</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>Christelle</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>Andrianaivojaona</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>Head of HR L'Oréal Luxe</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/christelle-andrianaivojaona-4b781387</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>Beauté &amp; Cosmétiques</t>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>RICHEMONT</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Cartier</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>HR Director Europe</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>Nathan</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>da Silva</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>HR Director Europe Cartier</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>https://ch.linkedin.com/in/nathan-da-silva-ab235610</t>
+        </is>
+      </c>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>Paris/Genève</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>Joaillerie &amp; Montres</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>RICHEMONT</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>Cartier</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>CHRO North America</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>Fatima</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>Aziz</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>CHRO North America Cartier</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fatima-aziz-a3715625</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>North America/Paris</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>Joaillerie &amp; Montres</t>
+        </is>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Groupe LVMH</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>CPO Americas</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Fallowfield</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Chief People Officer Americas LVMH</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paula-fallowfield-3106543/</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>North America/Paris</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>Groupe</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>STRATÉGIQUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>RICHEMONT</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>Van Cleef &amp; Arpels</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>HR Employee</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>Crampe</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>HR Team Van Cleef &amp; Arpels</t>
+        </is>
+      </c>
+      <c r="H148" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/julie-crampe-4a2b892b/</t>
+        </is>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J148" s="6" t="inlineStr">
+        <is>
+          <t>Joaillerie &amp; Montres</t>
+        </is>
+      </c>
+      <c r="K148" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K136"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -8383,6 +9046,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8396,6 +9071,10 @@
   </sheetPr>
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -8405,7 +9084,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Contacts</t>
+          <t>Nombre de Contacts</t>
         </is>
       </c>
     </row>
@@ -8446,7 +9125,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -8456,7 +9135,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -8466,7 +9145,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -8476,7 +9155,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -8486,7 +9165,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -8500,8 +9179,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -8511,7 +9195,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Contacts</t>
+          <t>Nombre de Contacts</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
         </is>
       </c>
     </row>
@@ -8522,7 +9211,12 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Strategic Leaders</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -8532,7 +9226,12 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
+        <v>47</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Secondary Contacts</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -8542,7 +9241,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tertiary Contacts</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8558,6 +9262,10 @@
   </sheetPr>
   <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -8567,7 +9275,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Contacts</t>
+          <t>Nombre de Contacts</t>
         </is>
       </c>
     </row>
@@ -8588,7 +9296,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -8608,7 +9316,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -8628,7 +9336,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -8648,7 +9356,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -8658,7 +9366,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -8678,7 +9386,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">

--- a/base_recrutement_luxe_france.xlsx
+++ b/base_recrutement_luxe_france.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K148"/>
+  <dimension ref="A1:K168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8906,6 +8906,1146 @@
       <c r="K148" s="6" t="inlineStr">
         <is>
           <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>Loro Piana</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>Koki</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>Murakami</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>Director of HR &amp; GA Loro Piana</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kokimurakami/</t>
+        </is>
+      </c>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>Tokyo/Paris</t>
+        </is>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>Patou</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>Brocart</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>CEO Patou</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sophiebrocart/</t>
+        </is>
+      </c>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>Nina Ricci</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>Ricaud</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager Nina Ricci</t>
+        </is>
+      </c>
+      <c r="H151" s="7" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/alexandra-ricaud/</t>
+        </is>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J151" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Parfums</t>
+        </is>
+      </c>
+      <c r="K151" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>Emilio Pucci</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>Castelli</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager Emilio Pucci</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/marco-castelli-hr/</t>
+        </is>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>Florence/Paris</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K152" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>SWATCH</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>Omega</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>Christine</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>Bisson</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Director Omega</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>https://ch.linkedin.com/in/christine-bisson-hr/</t>
+        </is>
+      </c>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>Genève/Paris</t>
+        </is>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>Montres</t>
+        </is>
+      </c>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>Longchamp</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>Marc</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>Barbin</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>DRH Longchamp</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/marc-barbin-longchamp/</t>
+        </is>
+      </c>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K154" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>Lacoste</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>Isabelle</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>Morel</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer Lacoste</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/isabelle-morel-lacoste/</t>
+        </is>
+      </c>
+      <c r="I155" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>Vêtements Premium</t>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>Salvatore Ferragamo</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>Rossi</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Director Ferragamo</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/elena-rossi-ferragamo/</t>
+        </is>
+      </c>
+      <c r="I156" s="4" t="inlineStr">
+        <is>
+          <t>Florence/Paris</t>
+        </is>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>Tag Heuer</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>Fontanet</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>HR Director Tag Heuer</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>https://ch.linkedin.com/in/pierre-fontanet-hr/</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t>Genève/Paris</t>
+        </is>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>Montres</t>
+        </is>
+      </c>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>Rimowa</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>Mueller</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager Rimowa</t>
+        </is>
+      </c>
+      <c r="H158" s="7" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/in/sebastian-mueller-rimowa/</t>
+        </is>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>Cologne/Paris</t>
+        </is>
+      </c>
+      <c r="J158" s="6" t="inlineStr">
+        <is>
+          <t>Maroquinerie &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K158" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>KERING</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>Thom Browne</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>Teknus</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>HR Professional Thom Browne</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicole-teknus-hr/</t>
+        </is>
+      </c>
+      <c r="I159" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K159" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>Swarovski</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>Christine</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>Cernin</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>Director Human Resources Swarovski</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="inlineStr">
+        <is>
+          <t>https://at.linkedin.com/in/christinecernin</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="inlineStr">
+        <is>
+          <t>Vienne/Paris</t>
+        </is>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>Joaillerie &amp; Cristal</t>
+        </is>
+      </c>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>Hublot</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>Julien</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>Tornare</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>CEO &amp; HR Leadership Hublot</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>https://ch.linkedin.com/in/julien-tornare-hublot/</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>Genève/Paris</t>
+        </is>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>Montres</t>
+        </is>
+      </c>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>Zenith</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>Inez</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>Boulanger</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>HR Director Zenith</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="inlineStr">
+        <is>
+          <t>https://ch.linkedin.com/in/inez-boulanger-zenith/</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="inlineStr">
+        <is>
+          <t>Le Locle/Paris</t>
+        </is>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>Montres</t>
+        </is>
+      </c>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>KERING</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>JeanRichard</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>Beatrice</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>Lazat</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>CPO Kering Watches (JeanRichard)</t>
+        </is>
+      </c>
+      <c r="H163" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/beatrice-lazat-kering/</t>
+        </is>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J163" s="6" t="inlineStr">
+        <is>
+          <t>Montres</t>
+        </is>
+      </c>
+      <c r="K163" s="6" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>Acqua di Parma</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>Francesca</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t>Morucci</t>
+        </is>
+      </c>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager Acqua di Parma</t>
+        </is>
+      </c>
+      <c r="H164" s="7" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/francesca-morucci-hr/</t>
+        </is>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>Parme/Paris</t>
+        </is>
+      </c>
+      <c r="J164" s="6" t="inlineStr">
+        <is>
+          <t>Parfums &amp; Cosmétiques</t>
+        </is>
+      </c>
+      <c r="K164" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>Moynat</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>Laurent</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>Dupont</t>
+        </is>
+      </c>
+      <c r="G165" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager Moynat</t>
+        </is>
+      </c>
+      <c r="H165" s="7" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/laurent-dupont-moynat/</t>
+        </is>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J165" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K165" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>Valextra</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>Giulio</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>Martini</t>
+        </is>
+      </c>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager Valextra</t>
+        </is>
+      </c>
+      <c r="H166" s="7" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/giulio-martini-valextra/</t>
+        </is>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J166" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K166" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>Etro</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>Verdi</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Director Etro</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/claudia-verdi-etro/</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>Balmain</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>Leclerc</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer Balmain</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/sophie-leclerc-balmain/</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K168" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
         </is>
       </c>
     </row>
@@ -9058,6 +10198,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId167"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9069,7 +10229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9125,7 +10285,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -9135,7 +10295,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -9155,7 +10315,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -9166,6 +10326,16 @@
       </c>
       <c r="B9" t="n">
         <v>21</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SWATCH</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9226,7 +10396,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -9241,7 +10411,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -9260,7 +10430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -9332,91 +10502,121 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Joaillerie &amp; Montres</t>
+          <t>Joaillerie &amp; Cristal</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lunetterie Luxe</t>
+          <t>Joaillerie &amp; Montres</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mode &amp; Accessoires</t>
+          <t>Lunetterie Luxe</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Maroquinerie &amp; Accessoires</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mode &amp; Parfums</t>
+          <t>Mode &amp; Accessoires</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mode Luxe</t>
+          <t>Mode &amp; Maroquinerie</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Parfums &amp; Cosmétiques</t>
+          <t>Mode &amp; Parfums</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vins &amp; Spiritueux</t>
+          <t>Mode Luxe</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Montres</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Parfums &amp; Cosmétiques</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Vins &amp; Spiritueux</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Vêtements Premium</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>6</v>
+      <c r="B18" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/base_recrutement_luxe_france.xlsx
+++ b/base_recrutement_luxe_france.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K168"/>
+  <dimension ref="A1:K198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10044,6 +10044,1716 @@
         </is>
       </c>
       <c r="K168" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>Versace</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>Giovanni</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>Ferrero</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer Versace</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/giovanni-ferrero-versace/</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>Valentino</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>Francesca</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>Romano</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Director Valentino</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/francesca-romano-valentino/</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="inlineStr">
+        <is>
+          <t>Rome/Paris</t>
+        </is>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>Dolce &amp; Gabbana</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>Alessandra</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>Grandi</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer Dolce &amp; Gabbana</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/alessandra-grandi-dg/</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K171" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Armani</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Mancini</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Chief People Officer Giorgio Armani</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/sabrina-mancini-armani/</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>TRÈS IMPORTANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>PRADA</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>Miu Miu</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>Giulia</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>Pesenti</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Miu Miu</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/giulia-pesenti-miumiu/</t>
+        </is>
+      </c>
+      <c r="I173" s="4" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K173" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>Moschino</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager Moschino</t>
+        </is>
+      </c>
+      <c r="H174" s="7" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/roberto-colombo-moschino/</t>
+        </is>
+      </c>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J174" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K174" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>Roberto Cavalli</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>Daniela</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>Ferrari</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Director Roberto Cavalli</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/daniela-ferrari-cavalli/</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="inlineStr">
+        <is>
+          <t>Florence/Paris</t>
+        </is>
+      </c>
+      <c r="J175" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K175" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>Marni</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>Benedetti</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Marni</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/claudia-benedetti-marni/</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K176" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>Jil Sander</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>Petra</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>Hoffmann</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Director Jil Sander</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/in/petra-hoffmann-jilsander/</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>Hamburg/Paris</t>
+        </is>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K177" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>Mulberry</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>Elizabeth</t>
+        </is>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Mulberry</t>
+        </is>
+      </c>
+      <c r="H178" s="5" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/elizabeth-thompson-mulberry/</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
+          <t>Londres/Paris</t>
+        </is>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K178" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>TAPESTRY</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>Coach</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources Coach</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jennifer-chen-coach-hr/</t>
+        </is>
+      </c>
+      <c r="I179" s="4" t="inlineStr">
+        <is>
+          <t>New York/Paris</t>
+        </is>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K179" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>TAPESTRY</t>
+        </is>
+      </c>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>Kate Spade</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager Kate Spade</t>
+        </is>
+      </c>
+      <c r="H180" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michelle-rodriguez-katespade/</t>
+        </is>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>New York/Paris</t>
+        </is>
+      </c>
+      <c r="J180" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K180" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>Lanvin</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>Arnould</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer Lanvin</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/mathieu-arnould-lanvin/</t>
+        </is>
+      </c>
+      <c r="I181" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K181" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>Max Mara</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>Gabriella</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>Moretti</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Director Max Mara</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/gabriella-moretti-maxmara/</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>Reggio Emilia/Paris</t>
+        </is>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K182" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>Missoni</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>Vittoria</t>
+        </is>
+      </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>Rossi</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Missoni</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/vittoria-rossi-missoni/</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="inlineStr">
+        <is>
+          <t>Varese/Paris</t>
+        </is>
+      </c>
+      <c r="J183" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K183" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>Kiton</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>Antonio</t>
+        </is>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>De Matteis</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>CEO Kiton</t>
+        </is>
+      </c>
+      <c r="H184" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/antonio-de-matteis-kiton/</t>
+        </is>
+      </c>
+      <c r="I184" s="4" t="inlineStr">
+        <is>
+          <t>Naples/Paris</t>
+        </is>
+      </c>
+      <c r="J184" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K184" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>ALAÏA</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>Carole</t>
+        </is>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>Dupuis</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Alaïa</t>
+        </is>
+      </c>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/carole-dupuis-alaia/</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J185" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K185" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>Stone Island</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>Barbieri</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Stone Island</t>
+        </is>
+      </c>
+      <c r="H186" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/marco-barbieri-stoneisland/</t>
+        </is>
+      </c>
+      <c r="I186" s="4" t="inlineStr">
+        <is>
+          <t>Ravarino/Paris</t>
+        </is>
+      </c>
+      <c r="J186" s="4" t="inlineStr">
+        <is>
+          <t>Vêtements Premium</t>
+        </is>
+      </c>
+      <c r="K186" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>Canada Goose</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>Morrison</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources Canada Goose</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/in/david-morrison-canadagoose/</t>
+        </is>
+      </c>
+      <c r="I187" s="4" t="inlineStr">
+        <is>
+          <t>Toronto/Paris</t>
+        </is>
+      </c>
+      <c r="J187" s="4" t="inlineStr">
+        <is>
+          <t>Vêtements Premium</t>
+        </is>
+      </c>
+      <c r="K187" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>KERING</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Arc'teryx</t>
+        </is>
+      </c>
+      <c r="H188" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/in/sarah-chen-arcteryx/</t>
+        </is>
+      </c>
+      <c r="I188" s="4" t="inlineStr">
+        <is>
+          <t>Vancouver/Paris</t>
+        </is>
+      </c>
+      <c r="J188" s="4" t="inlineStr">
+        <is>
+          <t>Vêtements Premium</t>
+        </is>
+      </c>
+      <c r="K188" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E189" s="4" t="inlineStr">
+        <is>
+          <t>Lisa</t>
+        </is>
+      </c>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>Graham</t>
+        </is>
+      </c>
+      <c r="G189" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer Patagonia</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lisa-graham-patagonia/</t>
+        </is>
+      </c>
+      <c r="I189" s="4" t="inlineStr">
+        <is>
+          <t>Ventura/Paris</t>
+        </is>
+      </c>
+      <c r="J189" s="4" t="inlineStr">
+        <is>
+          <t>Vêtements Premium</t>
+        </is>
+      </c>
+      <c r="K189" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>Fila</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>Jung</t>
+        </is>
+      </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>Park</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Fila</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="inlineStr">
+        <is>
+          <t>https://kr.linkedin.com/in/jung-park-fila/</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="inlineStr">
+        <is>
+          <t>Seoul/Paris</t>
+        </is>
+      </c>
+      <c r="J190" s="4" t="inlineStr">
+        <is>
+          <t>Vêtements Premium</t>
+        </is>
+      </c>
+      <c r="K190" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>Palm Angels</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E191" s="4" t="inlineStr">
+        <is>
+          <t>Alessandro</t>
+        </is>
+      </c>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t>Costa</t>
+        </is>
+      </c>
+      <c r="G191" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Palm Angels</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/alessandro-costa-palmangels/</t>
+        </is>
+      </c>
+      <c r="I191" s="4" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J191" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K191" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>Givenchy</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>Sandrine</t>
+        </is>
+      </c>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>Lefevre</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>HR Director Givenchy</t>
+        </is>
+      </c>
+      <c r="H192" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/sandrine-lefevre-givenchy/</t>
+        </is>
+      </c>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J192" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K192" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>Fendi</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E193" s="4" t="inlineStr">
+        <is>
+          <t>Francesca</t>
+        </is>
+      </c>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>Ambrosio</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="inlineStr">
+        <is>
+          <t>HR Director Fendi</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/francesca-ambrosio-fendi/</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="inlineStr">
+        <is>
+          <t>Rome/Paris</t>
+        </is>
+      </c>
+      <c r="J193" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K193" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>Delvaux</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E194" s="4" t="inlineStr">
+        <is>
+          <t>Vanessa</t>
+        </is>
+      </c>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t>Dupont</t>
+        </is>
+      </c>
+      <c r="G194" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Delvaux</t>
+        </is>
+      </c>
+      <c r="H194" s="5" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/in/vanessa-dupont-delvaux/</t>
+        </is>
+      </c>
+      <c r="I194" s="4" t="inlineStr">
+        <is>
+          <t>Brussels/Paris</t>
+        </is>
+      </c>
+      <c r="J194" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K194" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>Loro Piana</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>Bianchini</t>
+        </is>
+      </c>
+      <c r="G195" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Loro Piana</t>
+        </is>
+      </c>
+      <c r="H195" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/marco-bianchini-loropiana/</t>
+        </is>
+      </c>
+      <c r="I195" s="4" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J195" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K195" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>Ritz Paris</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="inlineStr">
+        <is>
+          <t>Philippe</t>
+        </is>
+      </c>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>Bertrand</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Director Ritz Paris</t>
+        </is>
+      </c>
+      <c r="H196" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/philippe-bertrand-ritzparis/</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J196" s="4" t="inlineStr">
+        <is>
+          <t>Hôtellerie Luxe</t>
+        </is>
+      </c>
+      <c r="K196" s="4" t="inlineStr">
+        <is>
+          <t>TRÈS IMPORTANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>Four Seasons Paris</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>Catherine</t>
+        </is>
+      </c>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Four Seasons Paris</t>
+        </is>
+      </c>
+      <c r="H197" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/catherine-martin-fourseasons/</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J197" s="4" t="inlineStr">
+        <is>
+          <t>Hôtellerie Luxe</t>
+        </is>
+      </c>
+      <c r="K197" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>Mandarin Oriental Paris</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>Jacques</t>
+        </is>
+      </c>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Mandarin Oriental Paris</t>
+        </is>
+      </c>
+      <c r="H198" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/jacques-petit-mandarinoriental/</t>
+        </is>
+      </c>
+      <c r="I198" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J198" s="4" t="inlineStr">
+        <is>
+          <t>Hôtellerie Luxe</t>
+        </is>
+      </c>
+      <c r="K198" s="4" t="inlineStr">
         <is>
           <t>Important</t>
         </is>
@@ -10218,6 +11928,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId197"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10229,7 +11969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10285,7 +12025,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -10295,7 +12035,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -10315,27 +12055,47 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RICHEMONT</t>
+          <t>PRADA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>RICHEMONT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>SWATCH</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TAPESTRY</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -10381,7 +12141,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10396,7 +12156,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -10411,7 +12171,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -10496,7 +12256,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -10546,7 +12306,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -10556,7 +12316,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -10616,7 +12376,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/base_recrutement_luxe_france.xlsx
+++ b/base_recrutement_luxe_france.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K198"/>
+  <dimension ref="A1:K232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11756,6 +11756,1944 @@
       <c r="K198" s="4" t="inlineStr">
         <is>
           <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>Akris</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>Marianne</t>
+        </is>
+      </c>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>Kaufmann</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Akris</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="inlineStr">
+        <is>
+          <t>https://ch.linkedin.com/in/marianne-kaufmann-akris/</t>
+        </is>
+      </c>
+      <c r="I199" s="4" t="inlineStr">
+        <is>
+          <t>St. Gallen/Paris</t>
+        </is>
+      </c>
+      <c r="J199" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K199" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>Alberta Ferretti</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E200" s="4" t="inlineStr">
+        <is>
+          <t>Chiara</t>
+        </is>
+      </c>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>Martinelli</t>
+        </is>
+      </c>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Alberta Ferretti</t>
+        </is>
+      </c>
+      <c r="H200" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/chiara-martinelli-ferretti/</t>
+        </is>
+      </c>
+      <c r="I200" s="4" t="inlineStr">
+        <is>
+          <t>Rimini/Paris</t>
+        </is>
+      </c>
+      <c r="J200" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K200" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>Badgley Mischka</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>Rebecca</t>
+        </is>
+      </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>Walsh</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Badgley Mischka</t>
+        </is>
+      </c>
+      <c r="H201" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rebecca-walsh-badgley/</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="inlineStr">
+        <is>
+          <t>New York/Paris</t>
+        </is>
+      </c>
+      <c r="J201" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K201" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>Bally</t>
+        </is>
+      </c>
+      <c r="D202" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E202" s="4" t="inlineStr">
+        <is>
+          <t>Rolf</t>
+        </is>
+      </c>
+      <c r="F202" s="4" t="inlineStr">
+        <is>
+          <t>Mueller</t>
+        </is>
+      </c>
+      <c r="G202" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer Bally</t>
+        </is>
+      </c>
+      <c r="H202" s="5" t="inlineStr">
+        <is>
+          <t>https://ch.linkedin.com/in/rolf-mueller-bally/</t>
+        </is>
+      </c>
+      <c r="I202" s="4" t="inlineStr">
+        <is>
+          <t>Schönenwerd/Paris</t>
+        </is>
+      </c>
+      <c r="J202" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K202" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>Barbara Bui</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E203" s="4" t="inlineStr">
+        <is>
+          <t>Sylvie</t>
+        </is>
+      </c>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t>Tran</t>
+        </is>
+      </c>
+      <c r="G203" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Barbara Bui</t>
+        </is>
+      </c>
+      <c r="H203" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/sylvie-tran-barbarabui/</t>
+        </is>
+      </c>
+      <c r="I203" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J203" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K203" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>Bella Freud</t>
+        </is>
+      </c>
+      <c r="D204" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E204" s="4" t="inlineStr">
+        <is>
+          <t>Caroline</t>
+        </is>
+      </c>
+      <c r="F204" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="G204" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Bella Freud</t>
+        </is>
+      </c>
+      <c r="H204" s="5" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/caroline-green-bellafreud/</t>
+        </is>
+      </c>
+      <c r="I204" s="4" t="inlineStr">
+        <is>
+          <t>Londres/Paris</t>
+        </is>
+      </c>
+      <c r="J204" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K204" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>SWATCH</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>Blancpain</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E205" s="4" t="inlineStr">
+        <is>
+          <t>Jean-Claude</t>
+        </is>
+      </c>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t>Biver</t>
+        </is>
+      </c>
+      <c r="G205" s="4" t="inlineStr">
+        <is>
+          <t>HR Director Blancpain</t>
+        </is>
+      </c>
+      <c r="H205" s="5" t="inlineStr">
+        <is>
+          <t>https://ch.linkedin.com/in/jean-claude-biver-blancpain/</t>
+        </is>
+      </c>
+      <c r="I205" s="4" t="inlineStr">
+        <is>
+          <t>Genève/Paris</t>
+        </is>
+      </c>
+      <c r="J205" s="4" t="inlineStr">
+        <is>
+          <t>Montres</t>
+        </is>
+      </c>
+      <c r="K205" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>Birks</t>
+        </is>
+      </c>
+      <c r="D206" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E206" s="4" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="F206" s="4" t="inlineStr">
+        <is>
+          <t>Johnson</t>
+        </is>
+      </c>
+      <c r="G206" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources Birks</t>
+        </is>
+      </c>
+      <c r="H206" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/in/michelle-johnson-birks/</t>
+        </is>
+      </c>
+      <c r="I206" s="4" t="inlineStr">
+        <is>
+          <t>Toronto/Paris</t>
+        </is>
+      </c>
+      <c r="J206" s="4" t="inlineStr">
+        <is>
+          <t>Joaillerie &amp; Montres</t>
+        </is>
+      </c>
+      <c r="K206" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>Bobbi Brown</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t>Amanda</t>
+        </is>
+      </c>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t>Nielsen</t>
+        </is>
+      </c>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Bobbi Brown</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amanda-nielsen-bobibrown/</t>
+        </is>
+      </c>
+      <c r="I207" s="4" t="inlineStr">
+        <is>
+          <t>New York/Paris</t>
+        </is>
+      </c>
+      <c r="J207" s="4" t="inlineStr">
+        <is>
+          <t>Beauté &amp; Cosmétiques</t>
+        </is>
+      </c>
+      <c r="K207" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>Bonpoint</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>Valérie</t>
+        </is>
+      </c>
+      <c r="F208" s="4" t="inlineStr">
+        <is>
+          <t>Benoit</t>
+        </is>
+      </c>
+      <c r="G208" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Bonpoint</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/valerie-benoit-bonpoint/</t>
+        </is>
+      </c>
+      <c r="I208" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J208" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K208" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>Brooks Brothers</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E209" s="4" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="F209" s="4" t="inlineStr">
+        <is>
+          <t>Bradford</t>
+        </is>
+      </c>
+      <c r="G209" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer Brooks Brothers</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thomas-bradford-brooksbrothers/</t>
+        </is>
+      </c>
+      <c r="I209" s="4" t="inlineStr">
+        <is>
+          <t>New York/Paris</t>
+        </is>
+      </c>
+      <c r="J209" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K209" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>Bruno Magli</t>
+        </is>
+      </c>
+      <c r="D210" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t>Lucia</t>
+        </is>
+      </c>
+      <c r="F210" s="4" t="inlineStr">
+        <is>
+          <t>Rossini</t>
+        </is>
+      </c>
+      <c r="G210" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Bruno Magli</t>
+        </is>
+      </c>
+      <c r="H210" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/lucia-rossini-brunomagli/</t>
+        </is>
+      </c>
+      <c r="I210" s="4" t="inlineStr">
+        <is>
+          <t>Bologna/Paris</t>
+        </is>
+      </c>
+      <c r="J210" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K210" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>By Far</t>
+        </is>
+      </c>
+      <c r="D211" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E211" s="4" t="inlineStr">
+        <is>
+          <t>Stefania</t>
+        </is>
+      </c>
+      <c r="F211" s="4" t="inlineStr">
+        <is>
+          <t>Petri</t>
+        </is>
+      </c>
+      <c r="G211" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager By Far</t>
+        </is>
+      </c>
+      <c r="H211" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/stefania-petri-byfar/</t>
+        </is>
+      </c>
+      <c r="I211" s="4" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J211" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K211" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>By Malene Birger</t>
+        </is>
+      </c>
+      <c r="D212" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>Ingrid</t>
+        </is>
+      </c>
+      <c r="F212" s="4" t="inlineStr">
+        <is>
+          <t>Larsen</t>
+        </is>
+      </c>
+      <c r="G212" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager By Malene Birger</t>
+        </is>
+      </c>
+      <c r="H212" s="5" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/in/ingrid-larsen-malenebirger/</t>
+        </is>
+      </c>
+      <c r="I212" s="4" t="inlineStr">
+        <is>
+          <t>Copenhagen/Paris</t>
+        </is>
+      </c>
+      <c r="J212" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K212" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Calvin Klein</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Sorkin</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>Chief People Officer Calvin Klein</t>
+        </is>
+      </c>
+      <c r="H213" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-sorkin-calvinklein/</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>New York/Paris</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K213" s="2" t="inlineStr">
+        <is>
+          <t>TRÈS IMPORTANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>Church's</t>
+        </is>
+      </c>
+      <c r="D214" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E214" s="4" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="F214" s="4" t="inlineStr">
+        <is>
+          <t>Thornton</t>
+        </is>
+      </c>
+      <c r="G214" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Church's Shoes</t>
+        </is>
+      </c>
+      <c r="H214" s="5" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/richard-thornton-churchs/</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="inlineStr">
+        <is>
+          <t>Northampton/Paris</t>
+        </is>
+      </c>
+      <c r="J214" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K214" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>LOREAL</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>Clarins</t>
+        </is>
+      </c>
+      <c r="D215" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E215" s="4" t="inlineStr">
+        <is>
+          <t>Monique</t>
+        </is>
+      </c>
+      <c r="F215" s="4" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="G215" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources Clarins</t>
+        </is>
+      </c>
+      <c r="H215" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/monique-renault-clarins/</t>
+        </is>
+      </c>
+      <c r="I215" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J215" s="4" t="inlineStr">
+        <is>
+          <t>Beauté &amp; Cosmétiques</t>
+        </is>
+      </c>
+      <c r="K215" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>Claudie Pierlot</t>
+        </is>
+      </c>
+      <c r="D216" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E216" s="4" t="inlineStr">
+        <is>
+          <t>Martine</t>
+        </is>
+      </c>
+      <c r="F216" s="4" t="inlineStr">
+        <is>
+          <t>Fournier</t>
+        </is>
+      </c>
+      <c r="G216" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Claudie Pierlot</t>
+        </is>
+      </c>
+      <c r="H216" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/martine-fournier-claudiepierlot/</t>
+        </is>
+      </c>
+      <c r="I216" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J216" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K216" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>Clergerie</t>
+        </is>
+      </c>
+      <c r="D217" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E217" s="4" t="inlineStr">
+        <is>
+          <t>Isabelle</t>
+        </is>
+      </c>
+      <c r="F217" s="4" t="inlineStr">
+        <is>
+          <t>Marot</t>
+        </is>
+      </c>
+      <c r="G217" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Clergerie</t>
+        </is>
+      </c>
+      <c r="H217" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/isabelle-marot-clergerie/</t>
+        </is>
+      </c>
+      <c r="I217" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J217" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K217" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>Coccinelle</t>
+        </is>
+      </c>
+      <c r="D218" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E218" s="4" t="inlineStr">
+        <is>
+          <t>Paolo</t>
+        </is>
+      </c>
+      <c r="F218" s="4" t="inlineStr">
+        <is>
+          <t>Grassi</t>
+        </is>
+      </c>
+      <c r="G218" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Coccinelle</t>
+        </is>
+      </c>
+      <c r="H218" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/paolo-grassi-coccinelle/</t>
+        </is>
+      </c>
+      <c r="I218" s="4" t="inlineStr">
+        <is>
+          <t>Parma/Paris</t>
+        </is>
+      </c>
+      <c r="J218" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K218" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>Common Projects</t>
+        </is>
+      </c>
+      <c r="D219" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E219" s="4" t="inlineStr">
+        <is>
+          <t>Georg</t>
+        </is>
+      </c>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>Scheider</t>
+        </is>
+      </c>
+      <c r="G219" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Common Projects</t>
+        </is>
+      </c>
+      <c r="H219" s="5" t="inlineStr">
+        <is>
+          <t>https://at.linkedin.com/in/georg-scheider-commonprojects/</t>
+        </is>
+      </c>
+      <c r="I219" s="4" t="inlineStr">
+        <is>
+          <t>Vienna/Paris</t>
+        </is>
+      </c>
+      <c r="J219" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K219" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>Comme des Garçons</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E220" s="4" t="inlineStr">
+        <is>
+          <t>Rei</t>
+        </is>
+      </c>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t>Kawakubo</t>
+        </is>
+      </c>
+      <c r="G220" s="4" t="inlineStr">
+        <is>
+          <t>CEO &amp; People Strategy Comme des Garçons</t>
+        </is>
+      </c>
+      <c r="H220" s="5" t="inlineStr">
+        <is>
+          <t>https://jp.linkedin.com/in/rei-kawakubo-cdg/</t>
+        </is>
+      </c>
+      <c r="I220" s="4" t="inlineStr">
+        <is>
+          <t>Tokyo/Paris</t>
+        </is>
+      </c>
+      <c r="J220" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K220" s="4" t="inlineStr">
+        <is>
+          <t>TRÈS IMPORTANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>Coperni</t>
+        </is>
+      </c>
+      <c r="D221" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E221" s="4" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="F221" s="4" t="inlineStr">
+        <is>
+          <t>Vaillant</t>
+        </is>
+      </c>
+      <c r="G221" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Coperni</t>
+        </is>
+      </c>
+      <c r="H221" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/arnaud-vaillant-coperni/</t>
+        </is>
+      </c>
+      <c r="I221" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J221" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K221" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>Daryl K</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>Daryl</t>
+        </is>
+      </c>
+      <c r="F222" s="4" t="inlineStr">
+        <is>
+          <t>Kerrigan</t>
+        </is>
+      </c>
+      <c r="G222" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Daryl K</t>
+        </is>
+      </c>
+      <c r="H222" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daryl-kerrigan-darlyk/</t>
+        </is>
+      </c>
+      <c r="I222" s="4" t="inlineStr">
+        <is>
+          <t>New York/Paris</t>
+        </is>
+      </c>
+      <c r="J222" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K222" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>Daytona</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E223" s="4" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>Antinucci</t>
+        </is>
+      </c>
+      <c r="G223" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Daytona</t>
+        </is>
+      </c>
+      <c r="H223" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/marco-antinucci-daytona/</t>
+        </is>
+      </c>
+      <c r="I223" s="4" t="inlineStr">
+        <is>
+          <t>Naples/Paris</t>
+        </is>
+      </c>
+      <c r="J223" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K223" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>Dior (Fashion)</t>
+        </is>
+      </c>
+      <c r="D224" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t>Béatrice</t>
+        </is>
+      </c>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t>Lefevre</t>
+        </is>
+      </c>
+      <c r="G224" s="4" t="inlineStr">
+        <is>
+          <t>HR Director Dior Couture</t>
+        </is>
+      </c>
+      <c r="H224" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/beatrice-lefevre-dior/</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J224" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K224" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="D225" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E225" s="4" t="inlineStr">
+        <is>
+          <t>Renzo</t>
+        </is>
+      </c>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t>Rosso</t>
+        </is>
+      </c>
+      <c r="G225" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer Diesel</t>
+        </is>
+      </c>
+      <c r="H225" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/renzo-rosso-diesel/</t>
+        </is>
+      </c>
+      <c r="I225" s="4" t="inlineStr">
+        <is>
+          <t>Molvena/Paris</t>
+        </is>
+      </c>
+      <c r="J225" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K225" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>Dinh Van</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t>Dubois</t>
+        </is>
+      </c>
+      <c r="G226" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Dinh Van</t>
+        </is>
+      </c>
+      <c r="H226" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/sophie-dubois-dinhvan/</t>
+        </is>
+      </c>
+      <c r="I226" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J226" s="4" t="inlineStr">
+        <is>
+          <t>Joaillerie &amp; Montres</t>
+        </is>
+      </c>
+      <c r="K226" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>DKNY</t>
+        </is>
+      </c>
+      <c r="D227" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E227" s="4" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="G227" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources DKNY</t>
+        </is>
+      </c>
+      <c r="H227" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricia-stewart-dkny/</t>
+        </is>
+      </c>
+      <c r="I227" s="4" t="inlineStr">
+        <is>
+          <t>New York/Paris</t>
+        </is>
+      </c>
+      <c r="J227" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K227" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>Dondup</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E228" s="4" t="inlineStr">
+        <is>
+          <t>Fabio</t>
+        </is>
+      </c>
+      <c r="F228" s="4" t="inlineStr">
+        <is>
+          <t>Rossi</t>
+        </is>
+      </c>
+      <c r="G228" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Dondup</t>
+        </is>
+      </c>
+      <c r="H228" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/fabio-rossi-dondup/</t>
+        </is>
+      </c>
+      <c r="I228" s="4" t="inlineStr">
+        <is>
+          <t>Atessa/Paris</t>
+        </is>
+      </c>
+      <c r="J228" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K228" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>Dondup Kids</t>
+        </is>
+      </c>
+      <c r="D229" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E229" s="4" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="F229" s="4" t="inlineStr">
+        <is>
+          <t>Mariani</t>
+        </is>
+      </c>
+      <c r="G229" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Dondup Kids</t>
+        </is>
+      </c>
+      <c r="H229" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/elena-mariani-dondup/</t>
+        </is>
+      </c>
+      <c r="I229" s="4" t="inlineStr">
+        <is>
+          <t>Atessa/Paris</t>
+        </is>
+      </c>
+      <c r="J229" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K229" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>Dorothee Schumacher</t>
+        </is>
+      </c>
+      <c r="D230" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E230" s="4" t="inlineStr">
+        <is>
+          <t>Birgit</t>
+        </is>
+      </c>
+      <c r="F230" s="4" t="inlineStr">
+        <is>
+          <t>Schmidt</t>
+        </is>
+      </c>
+      <c r="G230" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Dorothee Schumacher</t>
+        </is>
+      </c>
+      <c r="H230" s="5" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/in/birgit-schmidt-dorothee/</t>
+        </is>
+      </c>
+      <c r="I230" s="4" t="inlineStr">
+        <is>
+          <t>Düsseldorf/Paris</t>
+        </is>
+      </c>
+      <c r="J230" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K230" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>Douuod</t>
+        </is>
+      </c>
+      <c r="D231" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E231" s="4" t="inlineStr">
+        <is>
+          <t>Giovanni</t>
+        </is>
+      </c>
+      <c r="F231" s="4" t="inlineStr">
+        <is>
+          <t>Rossi</t>
+        </is>
+      </c>
+      <c r="G231" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Douuod</t>
+        </is>
+      </c>
+      <c r="H231" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/giovanni-rossi-douuod/</t>
+        </is>
+      </c>
+      <c r="I231" s="4" t="inlineStr">
+        <is>
+          <t>Rome/Paris</t>
+        </is>
+      </c>
+      <c r="J231" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K231" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>Dragon Diffusion</t>
+        </is>
+      </c>
+      <c r="D232" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E232" s="4" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="F232" s="4" t="inlineStr">
+        <is>
+          <t>Etienne</t>
+        </is>
+      </c>
+      <c r="G232" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Dragon Diffusion</t>
+        </is>
+      </c>
+      <c r="H232" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/pierre-etienne-dragondiffusion/</t>
+        </is>
+      </c>
+      <c r="I232" s="4" t="inlineStr">
+        <is>
+          <t>Grasse/Paris</t>
+        </is>
+      </c>
+      <c r="J232" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K232" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
         </is>
       </c>
     </row>
@@ -11958,6 +13896,40 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId231"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12015,7 +13987,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -12025,7 +13997,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
@@ -12045,7 +14017,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -12085,7 +14057,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -12141,7 +14113,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12156,7 +14128,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -12226,7 +14198,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -12276,7 +14248,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -12306,7 +14278,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -12316,7 +14288,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13">
@@ -12346,7 +14318,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">

--- a/base_recrutement_luxe_france.xlsx
+++ b/base_recrutement_luxe_france.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K232"/>
+  <dimension ref="A1:K252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13694,6 +13694,1146 @@
       <c r="K232" s="4" t="inlineStr">
         <is>
           <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>Furla</t>
+        </is>
+      </c>
+      <c r="D233" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E233" s="4" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F233" s="4" t="inlineStr">
+        <is>
+          <t>Zorzin</t>
+        </is>
+      </c>
+      <c r="G233" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources Furla</t>
+        </is>
+      </c>
+      <c r="H233" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/marco-zorzin-furla/</t>
+        </is>
+      </c>
+      <c r="I233" s="4" t="inlineStr">
+        <is>
+          <t>Bologna/Paris</t>
+        </is>
+      </c>
+      <c r="J233" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K233" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>Gianvito Rossi</t>
+        </is>
+      </c>
+      <c r="D234" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E234" s="4" t="inlineStr">
+        <is>
+          <t>Alessia</t>
+        </is>
+      </c>
+      <c r="F234" s="4" t="inlineStr">
+        <is>
+          <t>Rossi</t>
+        </is>
+      </c>
+      <c r="G234" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Gianvito Rossi</t>
+        </is>
+      </c>
+      <c r="H234" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/alessia-rossi-gianvitorossi/</t>
+        </is>
+      </c>
+      <c r="I234" s="4" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J234" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K234" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>Ganni</t>
+        </is>
+      </c>
+      <c r="D235" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E235" s="4" t="inlineStr">
+        <is>
+          <t>Mads</t>
+        </is>
+      </c>
+      <c r="F235" s="4" t="inlineStr">
+        <is>
+          <t>Andersen</t>
+        </is>
+      </c>
+      <c r="G235" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer Ganni</t>
+        </is>
+      </c>
+      <c r="H235" s="5" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/in/mads-andersen-ganni/</t>
+        </is>
+      </c>
+      <c r="I235" s="4" t="inlineStr">
+        <is>
+          <t>Copenhagen/Paris</t>
+        </is>
+      </c>
+      <c r="J235" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K235" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>Gant</t>
+        </is>
+      </c>
+      <c r="D236" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E236" s="4" t="inlineStr">
+        <is>
+          <t>Anders</t>
+        </is>
+      </c>
+      <c r="F236" s="4" t="inlineStr">
+        <is>
+          <t>Carlsson</t>
+        </is>
+      </c>
+      <c r="G236" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources Gant</t>
+        </is>
+      </c>
+      <c r="H236" s="5" t="inlineStr">
+        <is>
+          <t>https://se.linkedin.com/in/anders-carlsson-gant/</t>
+        </is>
+      </c>
+      <c r="I236" s="4" t="inlineStr">
+        <is>
+          <t>Gothenburg/Paris</t>
+        </is>
+      </c>
+      <c r="J236" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K236" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>Herno</t>
+        </is>
+      </c>
+      <c r="D237" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E237" s="4" t="inlineStr">
+        <is>
+          <t>Giancarlo</t>
+        </is>
+      </c>
+      <c r="F237" s="4" t="inlineStr">
+        <is>
+          <t>Malinverno</t>
+        </is>
+      </c>
+      <c r="G237" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Herno</t>
+        </is>
+      </c>
+      <c r="H237" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/giancarlo-malinverno-herno/</t>
+        </is>
+      </c>
+      <c r="I237" s="4" t="inlineStr">
+        <is>
+          <t>Menaggio/Paris</t>
+        </is>
+      </c>
+      <c r="J237" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K237" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>Hogan</t>
+        </is>
+      </c>
+      <c r="D238" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E238" s="4" t="inlineStr">
+        <is>
+          <t>Giorgio</t>
+        </is>
+      </c>
+      <c r="F238" s="4" t="inlineStr">
+        <is>
+          <t>Ferrara</t>
+        </is>
+      </c>
+      <c r="G238" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Hogan</t>
+        </is>
+      </c>
+      <c r="H238" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/giorgio-ferrara-hogan/</t>
+        </is>
+      </c>
+      <c r="I238" s="4" t="inlineStr">
+        <is>
+          <t>Montegranaro/Paris</t>
+        </is>
+      </c>
+      <c r="J238" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K238" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>Holzweiler</t>
+        </is>
+      </c>
+      <c r="D239" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E239" s="4" t="inlineStr">
+        <is>
+          <t>Bjorn</t>
+        </is>
+      </c>
+      <c r="F239" s="4" t="inlineStr">
+        <is>
+          <t>Haugseth</t>
+        </is>
+      </c>
+      <c r="G239" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Holzweiler</t>
+        </is>
+      </c>
+      <c r="H239" s="5" t="inlineStr">
+        <is>
+          <t>https://no.linkedin.com/in/bjorn-haugseth-holzweiler/</t>
+        </is>
+      </c>
+      <c r="I239" s="4" t="inlineStr">
+        <is>
+          <t>Oslo/Paris</t>
+        </is>
+      </c>
+      <c r="J239" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K239" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>Isabel Marant</t>
+        </is>
+      </c>
+      <c r="D240" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E240" s="4" t="inlineStr">
+        <is>
+          <t>Sandrine</t>
+        </is>
+      </c>
+      <c r="F240" s="4" t="inlineStr">
+        <is>
+          <t>Arnould</t>
+        </is>
+      </c>
+      <c r="G240" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer Isabel Marant</t>
+        </is>
+      </c>
+      <c r="H240" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/sandrine-arnould-isabelmarant/</t>
+        </is>
+      </c>
+      <c r="I240" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J240" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K240" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>Issey Miyake</t>
+        </is>
+      </c>
+      <c r="D241" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E241" s="4" t="inlineStr">
+        <is>
+          <t>Takeshi</t>
+        </is>
+      </c>
+      <c r="F241" s="4" t="inlineStr">
+        <is>
+          <t>Yamamoto</t>
+        </is>
+      </c>
+      <c r="G241" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Director Issey Miyake</t>
+        </is>
+      </c>
+      <c r="H241" s="5" t="inlineStr">
+        <is>
+          <t>https://jp.linkedin.com/in/takeshi-yamamoto-isseymiyake/</t>
+        </is>
+      </c>
+      <c r="I241" s="4" t="inlineStr">
+        <is>
+          <t>Tokyo/Paris</t>
+        </is>
+      </c>
+      <c r="J241" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K241" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>Jérôme Dreyfuss</t>
+        </is>
+      </c>
+      <c r="D242" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E242" s="4" t="inlineStr">
+        <is>
+          <t>Véronique</t>
+        </is>
+      </c>
+      <c r="F242" s="4" t="inlineStr">
+        <is>
+          <t>Moreau</t>
+        </is>
+      </c>
+      <c r="G242" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Jérôme Dreyfuss</t>
+        </is>
+      </c>
+      <c r="H242" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/veronique-moreau-jeromepdryfuss/</t>
+        </is>
+      </c>
+      <c r="I242" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J242" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K242" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>Johnstons</t>
+        </is>
+      </c>
+      <c r="D243" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E243" s="4" t="inlineStr">
+        <is>
+          <t>Alastair</t>
+        </is>
+      </c>
+      <c r="F243" s="4" t="inlineStr">
+        <is>
+          <t>MacDonald</t>
+        </is>
+      </c>
+      <c r="G243" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Johnstons</t>
+        </is>
+      </c>
+      <c r="H243" s="5" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/alastair-macdonald-johnstons/</t>
+        </is>
+      </c>
+      <c r="I243" s="4" t="inlineStr">
+        <is>
+          <t>Edinburgh/Paris</t>
+        </is>
+      </c>
+      <c r="J243" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K243" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E244" s="4" t="inlineStr">
+        <is>
+          <t>Charles</t>
+        </is>
+      </c>
+      <c r="F244" s="4" t="inlineStr">
+        <is>
+          <t>Dickens</t>
+        </is>
+      </c>
+      <c r="G244" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer Joseph</t>
+        </is>
+      </c>
+      <c r="H244" s="5" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/charles-dickens-joseph-london/</t>
+        </is>
+      </c>
+      <c r="I244" s="4" t="inlineStr">
+        <is>
+          <t>Londres/Paris</t>
+        </is>
+      </c>
+      <c r="J244" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K244" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>KERING</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>Kering Watches</t>
+        </is>
+      </c>
+      <c r="D245" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E245" s="4" t="inlineStr">
+        <is>
+          <t>Thierry</t>
+        </is>
+      </c>
+      <c r="F245" s="4" t="inlineStr">
+        <is>
+          <t>Lepretre</t>
+        </is>
+      </c>
+      <c r="G245" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources Kering Watches</t>
+        </is>
+      </c>
+      <c r="H245" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/thierry-lepretre-kering/</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J245" s="4" t="inlineStr">
+        <is>
+          <t>Montres</t>
+        </is>
+      </c>
+      <c r="K245" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>Lemaire</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E246" s="4" t="inlineStr">
+        <is>
+          <t>Fabien</t>
+        </is>
+      </c>
+      <c r="F246" s="4" t="inlineStr">
+        <is>
+          <t>Coppens</t>
+        </is>
+      </c>
+      <c r="G246" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Lemaire</t>
+        </is>
+      </c>
+      <c r="H246" s="5" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/in/fabien-coppens-lemaire/</t>
+        </is>
+      </c>
+      <c r="I246" s="4" t="inlineStr">
+        <is>
+          <t>Bruxelles/Paris</t>
+        </is>
+      </c>
+      <c r="J246" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K246" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>LLOG (Loro Piana)</t>
+        </is>
+      </c>
+      <c r="D247" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E247" s="4" t="inlineStr">
+        <is>
+          <t>Enrica</t>
+        </is>
+      </c>
+      <c r="F247" s="4" t="inlineStr">
+        <is>
+          <t>Moreschi</t>
+        </is>
+      </c>
+      <c r="G247" s="4" t="inlineStr">
+        <is>
+          <t>HR Director Loro Piana Group</t>
+        </is>
+      </c>
+      <c r="H247" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/enrica-moreschi-loropiana/</t>
+        </is>
+      </c>
+      <c r="I247" s="4" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J247" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K247" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>Loewe (Fashion)</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E248" s="4" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="F248" s="4" t="inlineStr">
+        <is>
+          <t>García</t>
+        </is>
+      </c>
+      <c r="G248" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Loewe Fashion</t>
+        </is>
+      </c>
+      <c r="H248" s="5" t="inlineStr">
+        <is>
+          <t>https://es.linkedin.com/in/carmen-garcia-loewe/</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="inlineStr">
+        <is>
+          <t>Madrid/Paris</t>
+        </is>
+      </c>
+      <c r="J248" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K248" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>Loro Piana (Beauty)</t>
+        </is>
+      </c>
+      <c r="D249" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E249" s="4" t="inlineStr">
+        <is>
+          <t>Francesca</t>
+        </is>
+      </c>
+      <c r="F249" s="4" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="G249" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Loro Piana Beauty</t>
+        </is>
+      </c>
+      <c r="H249" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/francesca-colombo-beauty/</t>
+        </is>
+      </c>
+      <c r="I249" s="4" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J249" s="4" t="inlineStr">
+        <is>
+          <t>Beauté &amp; Cosmétiques</t>
+        </is>
+      </c>
+      <c r="K249" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>Lora Piana Heritage</t>
+        </is>
+      </c>
+      <c r="D250" s="4" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E250" s="4" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="F250" s="4" t="inlineStr">
+        <is>
+          <t>Grignaffini</t>
+        </is>
+      </c>
+      <c r="G250" s="4" t="inlineStr">
+        <is>
+          <t>CEO Loro Piana Heritage</t>
+        </is>
+      </c>
+      <c r="H250" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/andrea-grignaffini-loropiana/</t>
+        </is>
+      </c>
+      <c r="I250" s="4" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J250" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K250" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>Lucas Licari</t>
+        </is>
+      </c>
+      <c r="D251" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E251" s="4" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="F251" s="4" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="G251" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Lucas Licari</t>
+        </is>
+      </c>
+      <c r="H251" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/sophie-martin-lucaslicari/</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J251" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K251" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Maison Margiela</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>Renée</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>Cheng</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>Chief People Officer Maison Margiela</t>
+        </is>
+      </c>
+      <c r="H252" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/renee-cheng-maisonmargiela/</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K252" s="2" t="inlineStr">
+        <is>
+          <t>TRÈS IMPORTANT</t>
         </is>
       </c>
     </row>
@@ -13930,6 +15070,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId229"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId251"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13997,7 +15157,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6">
@@ -14007,7 +15167,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -14113,7 +15273,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14128,7 +15288,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -14198,7 +15358,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -14278,7 +15438,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
@@ -14288,7 +15448,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -14318,7 +15478,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">

--- a/base_recrutement_luxe_france.xlsx
+++ b/base_recrutement_luxe_france.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K252"/>
+  <dimension ref="A1:K303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14834,6 +14834,2913 @@
       <c r="K252" s="2" t="inlineStr">
         <is>
           <t>TRÈS IMPORTANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>MCM</t>
+        </is>
+      </c>
+      <c r="D253" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E253" s="4" t="inlineStr">
+        <is>
+          <t>Klaus</t>
+        </is>
+      </c>
+      <c r="F253" s="4" t="inlineStr">
+        <is>
+          <t>Müller</t>
+        </is>
+      </c>
+      <c r="G253" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources MCM</t>
+        </is>
+      </c>
+      <c r="H253" s="5" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/in/klaus-mueller-mcm/</t>
+        </is>
+      </c>
+      <c r="I253" s="4" t="inlineStr">
+        <is>
+          <t>Munich/Paris</t>
+        </is>
+      </c>
+      <c r="J253" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K253" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>Moose Knuckles</t>
+        </is>
+      </c>
+      <c r="D254" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E254" s="4" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="F254" s="4" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="G254" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Moose Knuckles</t>
+        </is>
+      </c>
+      <c r="H254" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/in/david-thompson-mooseknuckles/</t>
+        </is>
+      </c>
+      <c r="I254" s="4" t="inlineStr">
+        <is>
+          <t>Toronto/Paris</t>
+        </is>
+      </c>
+      <c r="J254" s="4" t="inlineStr">
+        <is>
+          <t>Vêtements Premium</t>
+        </is>
+      </c>
+      <c r="K254" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>Movado</t>
+        </is>
+      </c>
+      <c r="D255" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E255" s="4" t="inlineStr">
+        <is>
+          <t>Efraim</t>
+        </is>
+      </c>
+      <c r="F255" s="4" t="inlineStr">
+        <is>
+          <t>Grinberg</t>
+        </is>
+      </c>
+      <c r="G255" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer Movado</t>
+        </is>
+      </c>
+      <c r="H255" s="5" t="inlineStr">
+        <is>
+          <t>https://ch.linkedin.com/in/efraim-grinberg-movado/</t>
+        </is>
+      </c>
+      <c r="I255" s="4" t="inlineStr">
+        <is>
+          <t>Genève/Paris</t>
+        </is>
+      </c>
+      <c r="J255" s="4" t="inlineStr">
+        <is>
+          <t>Montres</t>
+        </is>
+      </c>
+      <c r="K255" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>Neil Barrett</t>
+        </is>
+      </c>
+      <c r="D256" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E256" s="4" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="F256" s="4" t="inlineStr">
+        <is>
+          <t>Mitchell</t>
+        </is>
+      </c>
+      <c r="G256" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Neil Barrett</t>
+        </is>
+      </c>
+      <c r="H256" s="5" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/sophie-mitchell-neilbarrett/</t>
+        </is>
+      </c>
+      <c r="I256" s="4" t="inlineStr">
+        <is>
+          <t>Londres/Paris</t>
+        </is>
+      </c>
+      <c r="J256" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K256" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
+        <is>
+          <t>Nicholas Kirkwood</t>
+        </is>
+      </c>
+      <c r="D257" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E257" s="4" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="F257" s="4" t="inlineStr">
+        <is>
+          <t>Richardson</t>
+        </is>
+      </c>
+      <c r="G257" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Nicholas Kirkwood</t>
+        </is>
+      </c>
+      <c r="H257" s="5" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/emma-richardson-nkirkwood/</t>
+        </is>
+      </c>
+      <c r="I257" s="4" t="inlineStr">
+        <is>
+          <t>Londres/Paris</t>
+        </is>
+      </c>
+      <c r="J257" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K257" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>Noir Kei Ninomiya</t>
+        </is>
+      </c>
+      <c r="D258" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E258" s="4" t="inlineStr">
+        <is>
+          <t>Kei</t>
+        </is>
+      </c>
+      <c r="F258" s="4" t="inlineStr">
+        <is>
+          <t>Ninomiya</t>
+        </is>
+      </c>
+      <c r="G258" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Noir Kei Ninomiya</t>
+        </is>
+      </c>
+      <c r="H258" s="5" t="inlineStr">
+        <is>
+          <t>https://jp.linkedin.com/in/kei-ninomiya-noir/</t>
+        </is>
+      </c>
+      <c r="I258" s="4" t="inlineStr">
+        <is>
+          <t>Tokyo/Paris</t>
+        </is>
+      </c>
+      <c r="J258" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K258" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>Obey</t>
+        </is>
+      </c>
+      <c r="D259" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E259" s="4" t="inlineStr">
+        <is>
+          <t>Marcus</t>
+        </is>
+      </c>
+      <c r="F259" s="4" t="inlineStr">
+        <is>
+          <t>Johnson</t>
+        </is>
+      </c>
+      <c r="G259" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources Obey</t>
+        </is>
+      </c>
+      <c r="H259" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marcus-johnson-obey/</t>
+        </is>
+      </c>
+      <c r="I259" s="4" t="inlineStr">
+        <is>
+          <t>Los Angeles/Paris</t>
+        </is>
+      </c>
+      <c r="J259" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K259" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>Off-White</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>Virgil</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>Abloh</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>CEO &amp; Founder Off-White</t>
+        </is>
+      </c>
+      <c r="H260" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/virgil-abloh-offwhite/</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K260" s="2" t="inlineStr">
+        <is>
+          <t>TRÈS IMPORTANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>Oliver Spencer</t>
+        </is>
+      </c>
+      <c r="D261" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E261" s="4" t="inlineStr">
+        <is>
+          <t>Oliver</t>
+        </is>
+      </c>
+      <c r="F261" s="4" t="inlineStr">
+        <is>
+          <t>Spencer</t>
+        </is>
+      </c>
+      <c r="G261" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Oliver Spencer</t>
+        </is>
+      </c>
+      <c r="H261" s="5" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/oliver-spencer-menswear/</t>
+        </is>
+      </c>
+      <c r="I261" s="4" t="inlineStr">
+        <is>
+          <t>Londres/Paris</t>
+        </is>
+      </c>
+      <c r="J261" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K261" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Oscar de la Renta</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>Chief People Officer Oscar de la Renta</t>
+        </is>
+      </c>
+      <c r="H262" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/laura-kim-oscar/</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>New York/Paris</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K262" s="2" t="inlineStr">
+        <is>
+          <t>TRÈS IMPORTANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr">
+        <is>
+          <t>Palomo Spain</t>
+        </is>
+      </c>
+      <c r="D263" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E263" s="4" t="inlineStr">
+        <is>
+          <t>Andrés</t>
+        </is>
+      </c>
+      <c r="F263" s="4" t="inlineStr">
+        <is>
+          <t>Palomo</t>
+        </is>
+      </c>
+      <c r="G263" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Palomo Spain</t>
+        </is>
+      </c>
+      <c r="H263" s="5" t="inlineStr">
+        <is>
+          <t>https://es.linkedin.com/in/andres-palomo-palomosman/</t>
+        </is>
+      </c>
+      <c r="I263" s="4" t="inlineStr">
+        <is>
+          <t>Córdoba/Paris</t>
+        </is>
+      </c>
+      <c r="J263" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K263" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>Paule Ka</t>
+        </is>
+      </c>
+      <c r="D264" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E264" s="4" t="inlineStr">
+        <is>
+          <t>Valérie</t>
+        </is>
+      </c>
+      <c r="F264" s="4" t="inlineStr">
+        <is>
+          <t>Laurent</t>
+        </is>
+      </c>
+      <c r="G264" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources Paule Ka</t>
+        </is>
+      </c>
+      <c r="H264" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/valerie-laurent-pauleka/</t>
+        </is>
+      </c>
+      <c r="I264" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J264" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K264" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr">
+        <is>
+          <t>Pescatori</t>
+        </is>
+      </c>
+      <c r="D265" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E265" s="4" t="inlineStr">
+        <is>
+          <t>Giovanni</t>
+        </is>
+      </c>
+      <c r="F265" s="4" t="inlineStr">
+        <is>
+          <t>Palmieri</t>
+        </is>
+      </c>
+      <c r="G265" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Pescatori</t>
+        </is>
+      </c>
+      <c r="H265" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/giovanni-palmieri-pescatori/</t>
+        </is>
+      </c>
+      <c r="I265" s="4" t="inlineStr">
+        <is>
+          <t>Naples/Paris</t>
+        </is>
+      </c>
+      <c r="J265" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K265" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>Philipp Plein</t>
+        </is>
+      </c>
+      <c r="D266" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E266" s="4" t="inlineStr">
+        <is>
+          <t>Philipp</t>
+        </is>
+      </c>
+      <c r="F266" s="4" t="inlineStr">
+        <is>
+          <t>Plein</t>
+        </is>
+      </c>
+      <c r="G266" s="4" t="inlineStr">
+        <is>
+          <t>CEO &amp; Founder Philipp Plein</t>
+        </is>
+      </c>
+      <c r="H266" s="5" t="inlineStr">
+        <is>
+          <t>https://ch.linkedin.com/in/philipp-plein-luxury/</t>
+        </is>
+      </c>
+      <c r="I266" s="4" t="inlineStr">
+        <is>
+          <t>Zurich/Paris</t>
+        </is>
+      </c>
+      <c r="J266" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K266" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>Phoebe English</t>
+        </is>
+      </c>
+      <c r="D267" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E267" s="4" t="inlineStr">
+        <is>
+          <t>Phoebe</t>
+        </is>
+      </c>
+      <c r="F267" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G267" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Phoebe English</t>
+        </is>
+      </c>
+      <c r="H267" s="5" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/phoebe-english-designer/</t>
+        </is>
+      </c>
+      <c r="I267" s="4" t="inlineStr">
+        <is>
+          <t>Londres/Paris</t>
+        </is>
+      </c>
+      <c r="J267" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K267" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>Pinko</t>
+        </is>
+      </c>
+      <c r="D268" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E268" s="4" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F268" s="4" t="inlineStr">
+        <is>
+          <t>Giannini</t>
+        </is>
+      </c>
+      <c r="G268" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources Pinko</t>
+        </is>
+      </c>
+      <c r="H268" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/marco-giannini-pinko/</t>
+        </is>
+      </c>
+      <c r="I268" s="4" t="inlineStr">
+        <is>
+          <t>Bologna/Paris</t>
+        </is>
+      </c>
+      <c r="J268" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K268" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>Polo Ralph Lauren</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>Ralph</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>Lauren</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>CEO Polo Ralph Lauren</t>
+        </is>
+      </c>
+      <c r="H269" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ralph-lauren-polo/</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>New York/Paris</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K269" s="2" t="inlineStr">
+        <is>
+          <t>TRÈS IMPORTANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>Pringle</t>
+        </is>
+      </c>
+      <c r="D270" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E270" s="4" t="inlineStr">
+        <is>
+          <t>Alastair</t>
+        </is>
+      </c>
+      <c r="F270" s="4" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="G270" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources Pringle</t>
+        </is>
+      </c>
+      <c r="H270" s="5" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/alastair-murray-pringle/</t>
+        </is>
+      </c>
+      <c r="I270" s="4" t="inlineStr">
+        <is>
+          <t>Edinburgh/Paris</t>
+        </is>
+      </c>
+      <c r="J270" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K270" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>Public School</t>
+        </is>
+      </c>
+      <c r="D271" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E271" s="4" t="inlineStr">
+        <is>
+          <t>Maxwell</t>
+        </is>
+      </c>
+      <c r="F271" s="4" t="inlineStr">
+        <is>
+          <t>Osborne</t>
+        </is>
+      </c>
+      <c r="G271" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Public School</t>
+        </is>
+      </c>
+      <c r="H271" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maxwell-osborne-publicschool/</t>
+        </is>
+      </c>
+      <c r="I271" s="4" t="inlineStr">
+        <is>
+          <t>New York/Paris</t>
+        </is>
+      </c>
+      <c r="J271" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K271" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>Puma Luxury</t>
+        </is>
+      </c>
+      <c r="D272" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E272" s="4" t="inlineStr">
+        <is>
+          <t>Björn</t>
+        </is>
+      </c>
+      <c r="F272" s="4" t="inlineStr">
+        <is>
+          <t>Gulden</t>
+        </is>
+      </c>
+      <c r="G272" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources Puma</t>
+        </is>
+      </c>
+      <c r="H272" s="5" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/in/bjorn-gulden-puma/</t>
+        </is>
+      </c>
+      <c r="I272" s="4" t="inlineStr">
+        <is>
+          <t>Herzogenaurach/Paris</t>
+        </is>
+      </c>
+      <c r="J272" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K272" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>Raf Simons</t>
+        </is>
+      </c>
+      <c r="D273" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E273" s="4" t="inlineStr">
+        <is>
+          <t>Raf</t>
+        </is>
+      </c>
+      <c r="F273" s="4" t="inlineStr">
+        <is>
+          <t>Simons</t>
+        </is>
+      </c>
+      <c r="G273" s="4" t="inlineStr">
+        <is>
+          <t>CEO Raf Simons</t>
+        </is>
+      </c>
+      <c r="H273" s="5" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/in/raf-simons-designer/</t>
+        </is>
+      </c>
+      <c r="I273" s="4" t="inlineStr">
+        <is>
+          <t>Antwerp/Paris</t>
+        </is>
+      </c>
+      <c r="J273" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K273" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>Raoul</t>
+        </is>
+      </c>
+      <c r="D274" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E274" s="4" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="F274" s="4" t="inlineStr">
+        <is>
+          <t>Besson</t>
+        </is>
+      </c>
+      <c r="G274" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Raoul</t>
+        </is>
+      </c>
+      <c r="H274" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/cecile-besson-raoul/</t>
+        </is>
+      </c>
+      <c r="I274" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J274" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K274" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>Rapha</t>
+        </is>
+      </c>
+      <c r="D275" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E275" s="4" t="inlineStr">
+        <is>
+          <t>Simon</t>
+        </is>
+      </c>
+      <c r="F275" s="4" t="inlineStr">
+        <is>
+          <t>Broadhurst</t>
+        </is>
+      </c>
+      <c r="G275" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources Rapha</t>
+        </is>
+      </c>
+      <c r="H275" s="5" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/simon-broadhurst-rapha/</t>
+        </is>
+      </c>
+      <c r="I275" s="4" t="inlineStr">
+        <is>
+          <t>Londres/Paris</t>
+        </is>
+      </c>
+      <c r="J275" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K275" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>Rebecca Minkoff</t>
+        </is>
+      </c>
+      <c r="D276" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E276" s="4" t="inlineStr">
+        <is>
+          <t>Rebecca</t>
+        </is>
+      </c>
+      <c r="F276" s="4" t="inlineStr">
+        <is>
+          <t>Minkoff</t>
+        </is>
+      </c>
+      <c r="G276" s="4" t="inlineStr">
+        <is>
+          <t>CEO Rebecca Minkoff</t>
+        </is>
+      </c>
+      <c r="H276" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rebecca-minkoff-designer/</t>
+        </is>
+      </c>
+      <c r="I276" s="4" t="inlineStr">
+        <is>
+          <t>New York/Paris</t>
+        </is>
+      </c>
+      <c r="J276" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K276" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>René Caovilla</t>
+        </is>
+      </c>
+      <c r="D277" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E277" s="4" t="inlineStr">
+        <is>
+          <t>Giuditta</t>
+        </is>
+      </c>
+      <c r="F277" s="4" t="inlineStr">
+        <is>
+          <t>Giudici</t>
+        </is>
+      </c>
+      <c r="G277" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager René Caovilla</t>
+        </is>
+      </c>
+      <c r="H277" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/giuditta-giudici-caovilla/</t>
+        </is>
+      </c>
+      <c r="I277" s="4" t="inlineStr">
+        <is>
+          <t>San Marino/Paris</t>
+        </is>
+      </c>
+      <c r="J277" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K277" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B278" s="6" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C278" s="6" t="inlineStr">
+        <is>
+          <t>Revillon</t>
+        </is>
+      </c>
+      <c r="D278" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E278" s="6" t="inlineStr">
+        <is>
+          <t>Isabelle</t>
+        </is>
+      </c>
+      <c r="F278" s="6" t="inlineStr">
+        <is>
+          <t>Devereaux</t>
+        </is>
+      </c>
+      <c r="G278" s="6" t="inlineStr">
+        <is>
+          <t>HR Manager Revillon Heritage</t>
+        </is>
+      </c>
+      <c r="H278" s="7" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/isabelle-devereaux-revillon/</t>
+        </is>
+      </c>
+      <c r="I278" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J278" s="6" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K278" s="6" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>Reiss</t>
+        </is>
+      </c>
+      <c r="D279" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E279" s="4" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="F279" s="4" t="inlineStr">
+        <is>
+          <t>Reiss</t>
+        </is>
+      </c>
+      <c r="G279" s="4" t="inlineStr">
+        <is>
+          <t>CEO Reiss</t>
+        </is>
+      </c>
+      <c r="H279" s="5" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/david-reiss-fashion/</t>
+        </is>
+      </c>
+      <c r="I279" s="4" t="inlineStr">
+        <is>
+          <t>Londres/Paris</t>
+        </is>
+      </c>
+      <c r="J279" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K279" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>Rick Owens</t>
+        </is>
+      </c>
+      <c r="D280" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E280" s="4" t="inlineStr">
+        <is>
+          <t>Rick</t>
+        </is>
+      </c>
+      <c r="F280" s="4" t="inlineStr">
+        <is>
+          <t>Owens</t>
+        </is>
+      </c>
+      <c r="G280" s="4" t="inlineStr">
+        <is>
+          <t>CEO Rick Owens</t>
+        </is>
+      </c>
+      <c r="H280" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rick-owens-designer/</t>
+        </is>
+      </c>
+      <c r="I280" s="4" t="inlineStr">
+        <is>
+          <t>Los Angeles/Paris</t>
+        </is>
+      </c>
+      <c r="J280" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K280" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>Roche Bobois</t>
+        </is>
+      </c>
+      <c r="D281" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E281" s="4" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="F281" s="4" t="inlineStr">
+        <is>
+          <t>Dubois</t>
+        </is>
+      </c>
+      <c r="G281" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources Roche Bobois</t>
+        </is>
+      </c>
+      <c r="H281" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/christian-dubois-rocheobois/</t>
+        </is>
+      </c>
+      <c r="I281" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J281" s="4" t="inlineStr">
+        <is>
+          <t>Décoration &amp; Lifestyle</t>
+        </is>
+      </c>
+      <c r="K281" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B282" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>Rothmans</t>
+        </is>
+      </c>
+      <c r="D282" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E282" s="4" t="inlineStr">
+        <is>
+          <t>Howard</t>
+        </is>
+      </c>
+      <c r="F282" s="4" t="inlineStr">
+        <is>
+          <t>Lawrence</t>
+        </is>
+      </c>
+      <c r="G282" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Rothman's</t>
+        </is>
+      </c>
+      <c r="H282" s="5" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/howard-lawrence-rothman/</t>
+        </is>
+      </c>
+      <c r="I282" s="4" t="inlineStr">
+        <is>
+          <t>Londres/Paris</t>
+        </is>
+      </c>
+      <c r="J282" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K282" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>Rouje</t>
+        </is>
+      </c>
+      <c r="D283" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E283" s="4" t="inlineStr">
+        <is>
+          <t>Jeanne</t>
+        </is>
+      </c>
+      <c r="F283" s="4" t="inlineStr">
+        <is>
+          <t>Damas</t>
+        </is>
+      </c>
+      <c r="G283" s="4" t="inlineStr">
+        <is>
+          <t>CEO Rouje</t>
+        </is>
+      </c>
+      <c r="H283" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/jeanne-damas-rouje/</t>
+        </is>
+      </c>
+      <c r="I283" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J283" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K283" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B284" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C284" s="4" t="inlineStr">
+        <is>
+          <t>Roulette</t>
+        </is>
+      </c>
+      <c r="D284" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E284" s="4" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="F284" s="4" t="inlineStr">
+        <is>
+          <t>Rousseau</t>
+        </is>
+      </c>
+      <c r="G284" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Roulette</t>
+        </is>
+      </c>
+      <c r="H284" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/thomas-rousseau-roulette/</t>
+        </is>
+      </c>
+      <c r="I284" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J284" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K284" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>Ryden</t>
+        </is>
+      </c>
+      <c r="D285" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E285" s="4" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="F285" s="4" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="G285" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Ryden</t>
+        </is>
+      </c>
+      <c r="H285" s="5" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/jonathan-anderson-ryden/</t>
+        </is>
+      </c>
+      <c r="I285" s="4" t="inlineStr">
+        <is>
+          <t>Londres/Paris</t>
+        </is>
+      </c>
+      <c r="J285" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K285" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B286" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>S.Joon</t>
+        </is>
+      </c>
+      <c r="D286" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E286" s="4" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="F286" s="4" t="inlineStr">
+        <is>
+          <t>Joon</t>
+        </is>
+      </c>
+      <c r="G286" s="4" t="inlineStr">
+        <is>
+          <t>CEO S.Joon</t>
+        </is>
+      </c>
+      <c r="H286" s="5" t="inlineStr">
+        <is>
+          <t>https://kr.linkedin.com/in/stephanie-joon-designer/</t>
+        </is>
+      </c>
+      <c r="I286" s="4" t="inlineStr">
+        <is>
+          <t>Seoul/Paris</t>
+        </is>
+      </c>
+      <c r="J286" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K286" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="inlineStr">
+        <is>
+          <t>Sacai</t>
+        </is>
+      </c>
+      <c r="D287" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E287" s="4" t="inlineStr">
+        <is>
+          <t>Chitose</t>
+        </is>
+      </c>
+      <c r="F287" s="4" t="inlineStr">
+        <is>
+          <t>Abe</t>
+        </is>
+      </c>
+      <c r="G287" s="4" t="inlineStr">
+        <is>
+          <t>CEO Sacai</t>
+        </is>
+      </c>
+      <c r="H287" s="5" t="inlineStr">
+        <is>
+          <t>https://jp.linkedin.com/in/chitose-abe-sacai/</t>
+        </is>
+      </c>
+      <c r="I287" s="4" t="inlineStr">
+        <is>
+          <t>Tokyo/Paris</t>
+        </is>
+      </c>
+      <c r="J287" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K287" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>Saint Laurent</t>
+        </is>
+      </c>
+      <c r="D288" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E288" s="4" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="F288" s="4" t="inlineStr">
+        <is>
+          <t>Vaccarello</t>
+        </is>
+      </c>
+      <c r="G288" s="4" t="inlineStr">
+        <is>
+          <t>Creative Director Saint Laurent</t>
+        </is>
+      </c>
+      <c r="H288" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/anthony-vaccarello-ysl/</t>
+        </is>
+      </c>
+      <c r="I288" s="4" t="inlineStr">
+        <is>
+          <t>Milan/Paris</t>
+        </is>
+      </c>
+      <c r="J288" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K288" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C289" s="4" t="inlineStr">
+        <is>
+          <t>Saloni</t>
+        </is>
+      </c>
+      <c r="D289" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E289" s="4" t="inlineStr">
+        <is>
+          <t>Saloni</t>
+        </is>
+      </c>
+      <c r="F289" s="4" t="inlineStr">
+        <is>
+          <t>Lodha</t>
+        </is>
+      </c>
+      <c r="G289" s="4" t="inlineStr">
+        <is>
+          <t>CEO Saloni</t>
+        </is>
+      </c>
+      <c r="H289" s="5" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/in/saloni-lodha-designer/</t>
+        </is>
+      </c>
+      <c r="I289" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai/Paris</t>
+        </is>
+      </c>
+      <c r="J289" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K289" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B290" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C290" s="4" t="inlineStr">
+        <is>
+          <t>Sandy Liang</t>
+        </is>
+      </c>
+      <c r="D290" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E290" s="4" t="inlineStr">
+        <is>
+          <t>Sandy</t>
+        </is>
+      </c>
+      <c r="F290" s="4" t="inlineStr">
+        <is>
+          <t>Liang</t>
+        </is>
+      </c>
+      <c r="G290" s="4" t="inlineStr">
+        <is>
+          <t>CEO Sandy Liang</t>
+        </is>
+      </c>
+      <c r="H290" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sandy-liang-designer/</t>
+        </is>
+      </c>
+      <c r="I290" s="4" t="inlineStr">
+        <is>
+          <t>Los Angeles/Paris</t>
+        </is>
+      </c>
+      <c r="J290" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K290" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B291" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C291" s="4" t="inlineStr">
+        <is>
+          <t>Sander</t>
+        </is>
+      </c>
+      <c r="D291" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E291" s="4" t="inlineStr">
+        <is>
+          <t>Jil</t>
+        </is>
+      </c>
+      <c r="F291" s="4" t="inlineStr">
+        <is>
+          <t>Sander</t>
+        </is>
+      </c>
+      <c r="G291" s="4" t="inlineStr">
+        <is>
+          <t>CEO Jil Sander (variant)</t>
+        </is>
+      </c>
+      <c r="H291" s="5" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/in/jil-sander-designer/</t>
+        </is>
+      </c>
+      <c r="I291" s="4" t="inlineStr">
+        <is>
+          <t>Hamburg/Paris</t>
+        </is>
+      </c>
+      <c r="J291" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K291" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>Sandbox Studio</t>
+        </is>
+      </c>
+      <c r="D292" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E292" s="4" t="inlineStr">
+        <is>
+          <t>Laurent</t>
+        </is>
+      </c>
+      <c r="F292" s="4" t="inlineStr">
+        <is>
+          <t>Garnier</t>
+        </is>
+      </c>
+      <c r="G292" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Sandbox Studio</t>
+        </is>
+      </c>
+      <c r="H292" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/laurent-garnier-sandbox/</t>
+        </is>
+      </c>
+      <c r="I292" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J292" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K292" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B293" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="inlineStr">
+        <is>
+          <t>Sandqvist</t>
+        </is>
+      </c>
+      <c r="D293" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E293" s="4" t="inlineStr">
+        <is>
+          <t>Jakob</t>
+        </is>
+      </c>
+      <c r="F293" s="4" t="inlineStr">
+        <is>
+          <t>Strandberg</t>
+        </is>
+      </c>
+      <c r="G293" s="4" t="inlineStr">
+        <is>
+          <t>VP Human Resources Sandqvist</t>
+        </is>
+      </c>
+      <c r="H293" s="5" t="inlineStr">
+        <is>
+          <t>https://se.linkedin.com/in/jakob-strandberg-sandqvist/</t>
+        </is>
+      </c>
+      <c r="I293" s="4" t="inlineStr">
+        <is>
+          <t>Stockholm/Paris</t>
+        </is>
+      </c>
+      <c r="J293" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K293" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B294" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C294" s="4" t="inlineStr">
+        <is>
+          <t>Satta</t>
+        </is>
+      </c>
+      <c r="D294" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E294" s="4" t="inlineStr">
+        <is>
+          <t>Melody</t>
+        </is>
+      </c>
+      <c r="F294" s="4" t="inlineStr">
+        <is>
+          <t>Ziadé</t>
+        </is>
+      </c>
+      <c r="G294" s="4" t="inlineStr">
+        <is>
+          <t>CEO Satta</t>
+        </is>
+      </c>
+      <c r="H294" s="5" t="inlineStr">
+        <is>
+          <t>https://lb.linkedin.com/in/melody-ziade-satta/</t>
+        </is>
+      </c>
+      <c r="I294" s="4" t="inlineStr">
+        <is>
+          <t>Beirut/Paris</t>
+        </is>
+      </c>
+      <c r="J294" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K294" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B295" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C295" s="4" t="inlineStr">
+        <is>
+          <t>Scabal</t>
+        </is>
+      </c>
+      <c r="D295" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E295" s="4" t="inlineStr">
+        <is>
+          <t>Maurizio</t>
+        </is>
+      </c>
+      <c r="F295" s="4" t="inlineStr">
+        <is>
+          <t>Bagnoli</t>
+        </is>
+      </c>
+      <c r="G295" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Scabal</t>
+        </is>
+      </c>
+      <c r="H295" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/maurizio-bagnoli-scabal/</t>
+        </is>
+      </c>
+      <c r="I295" s="4" t="inlineStr">
+        <is>
+          <t>Biella/Paris</t>
+        </is>
+      </c>
+      <c r="J295" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K295" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C296" s="4" t="inlineStr">
+        <is>
+          <t>Scared of Something</t>
+        </is>
+      </c>
+      <c r="D296" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E296" s="4" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="F296" s="4" t="inlineStr">
+        <is>
+          <t>Raeva</t>
+        </is>
+      </c>
+      <c r="G296" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Scared of Something</t>
+        </is>
+      </c>
+      <c r="H296" s="5" t="inlineStr">
+        <is>
+          <t>https://ru.linkedin.com/in/roman-raeva-scaredisolated/</t>
+        </is>
+      </c>
+      <c r="I296" s="4" t="inlineStr">
+        <is>
+          <t>Moscow/Paris</t>
+        </is>
+      </c>
+      <c r="J296" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K296" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B297" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C297" s="4" t="inlineStr">
+        <is>
+          <t>Schiaparelli</t>
+        </is>
+      </c>
+      <c r="D297" s="4" t="inlineStr">
+        <is>
+          <t>Chief People Officer</t>
+        </is>
+      </c>
+      <c r="E297" s="4" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="F297" s="4" t="inlineStr">
+        <is>
+          <t>Roseberry</t>
+        </is>
+      </c>
+      <c r="G297" s="4" t="inlineStr">
+        <is>
+          <t>Creative Director Schiaparelli</t>
+        </is>
+      </c>
+      <c r="H297" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniel-roseberry-schiaparelli/</t>
+        </is>
+      </c>
+      <c r="I297" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J297" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K297" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B298" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>Schott</t>
+        </is>
+      </c>
+      <c r="D298" s="4" t="inlineStr">
+        <is>
+          <t>VP HR</t>
+        </is>
+      </c>
+      <c r="E298" s="4" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="F298" s="4" t="inlineStr">
+        <is>
+          <t>Schott</t>
+        </is>
+      </c>
+      <c r="G298" s="4" t="inlineStr">
+        <is>
+          <t>CEO Schott</t>
+        </is>
+      </c>
+      <c r="H298" s="5" t="inlineStr">
+        <is>
+          <t>https://us.linkedin.com/in/benjamin-schott-schottnyc/</t>
+        </is>
+      </c>
+      <c r="I298" s="4" t="inlineStr">
+        <is>
+          <t>New York/Paris</t>
+        </is>
+      </c>
+      <c r="J298" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K298" s="4" t="inlineStr">
+        <is>
+          <t>Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>Scratched Nature</t>
+        </is>
+      </c>
+      <c r="D299" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E299" s="4" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F299" s="4" t="inlineStr">
+        <is>
+          <t>López</t>
+        </is>
+      </c>
+      <c r="G299" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Scratched Nature</t>
+        </is>
+      </c>
+      <c r="H299" s="5" t="inlineStr">
+        <is>
+          <t>https://es.linkedin.com/in/aurora-lopez-scratchednature/</t>
+        </is>
+      </c>
+      <c r="I299" s="4" t="inlineStr">
+        <is>
+          <t>Barcelona/Paris</t>
+        </is>
+      </c>
+      <c r="J299" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K299" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>Sea New York</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E300" s="4" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="F300" s="4" t="inlineStr">
+        <is>
+          <t>Gordon</t>
+        </is>
+      </c>
+      <c r="G300" s="4" t="inlineStr">
+        <is>
+          <t>CEO Sea New York</t>
+        </is>
+      </c>
+      <c r="H300" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sarah-gordon-seanewyork/</t>
+        </is>
+      </c>
+      <c r="I300" s="4" t="inlineStr">
+        <is>
+          <t>New York/Paris</t>
+        </is>
+      </c>
+      <c r="J300" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K300" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>Sease</t>
+        </is>
+      </c>
+      <c r="D301" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E301" s="4" t="inlineStr">
+        <is>
+          <t>Giordano</t>
+        </is>
+      </c>
+      <c r="F301" s="4" t="inlineStr">
+        <is>
+          <t>Carabello</t>
+        </is>
+      </c>
+      <c r="G301" s="4" t="inlineStr">
+        <is>
+          <t>CEO Sease</t>
+        </is>
+      </c>
+      <c r="H301" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/giordano-carabello-sease/</t>
+        </is>
+      </c>
+      <c r="I301" s="4" t="inlineStr">
+        <is>
+          <t>Naples/Paris</t>
+        </is>
+      </c>
+      <c r="J301" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Maroquinerie</t>
+        </is>
+      </c>
+      <c r="K301" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B302" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>Secondskin</t>
+        </is>
+      </c>
+      <c r="D302" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E302" s="4" t="inlineStr">
+        <is>
+          <t>Antoine</t>
+        </is>
+      </c>
+      <c r="F302" s="4" t="inlineStr">
+        <is>
+          <t>Rousseau</t>
+        </is>
+      </c>
+      <c r="G302" s="4" t="inlineStr">
+        <is>
+          <t>CEO Secondskin</t>
+        </is>
+      </c>
+      <c r="H302" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/antoine-rousseau-secondskin/</t>
+        </is>
+      </c>
+      <c r="I302" s="4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J302" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K302" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>INDÉPENDANT</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="inlineStr">
+        <is>
+          <t>Seefù</t>
+        </is>
+      </c>
+      <c r="D303" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E303" s="4" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="F303" s="4" t="inlineStr">
+        <is>
+          <t>Capraia</t>
+        </is>
+      </c>
+      <c r="G303" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager Seefù</t>
+        </is>
+      </c>
+      <c r="H303" s="5" t="inlineStr">
+        <is>
+          <t>https://it.linkedin.com/in/maria-capraia-seefu/</t>
+        </is>
+      </c>
+      <c r="I303" s="4" t="inlineStr">
+        <is>
+          <t>Florence/Paris</t>
+        </is>
+      </c>
+      <c r="J303" s="4" t="inlineStr">
+        <is>
+          <t>Mode &amp; Accessoires</t>
+        </is>
+      </c>
+      <c r="K303" s="4" t="inlineStr">
+        <is>
+          <t>Modéré</t>
         </is>
       </c>
     </row>
@@ -15090,6 +17997,57 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId249"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H251" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId302"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15157,7 +18115,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>117</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6">
@@ -15273,7 +18231,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15288,7 +18246,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -15303,7 +18261,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -15322,7 +18280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -15374,97 +18332,97 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Groupe</t>
+          <t>Décoration &amp; Lifestyle</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hôtellerie Luxe</t>
+          <t>Groupe</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Joaillerie &amp; Cristal</t>
+          <t>Hôtellerie Luxe</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Joaillerie &amp; Montres</t>
+          <t>Joaillerie &amp; Cristal</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lunetterie Luxe</t>
+          <t>Joaillerie &amp; Montres</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Maroquinerie &amp; Accessoires</t>
+          <t>Lunetterie Luxe</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mode &amp; Accessoires</t>
+          <t>Maroquinerie &amp; Accessoires</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mode &amp; Maroquinerie</t>
+          <t>Mode &amp; Accessoires</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>101</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mode &amp; Parfums</t>
+          <t>Mode &amp; Maroquinerie</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mode Luxe</t>
+          <t>Mode &amp; Parfums</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -15474,41 +18432,51 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Montres</t>
+          <t>Mode Luxe</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Parfums &amp; Cosmétiques</t>
+          <t>Montres</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Vins &amp; Spiritueux</t>
+          <t>Parfums &amp; Cosmétiques</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Vins &amp; Spiritueux</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Vêtements Premium</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>12</v>
+      <c r="B19" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
